--- a/public/plantilla-inspecciones.xlsx
+++ b/public/plantilla-inspecciones.xlsx
@@ -3,19 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inspecciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="27">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,14 +71,6 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
@@ -170,14 +162,6 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="8.5"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
@@ -212,19 +196,114 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <sz val="7"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF1B2A45"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="8.5"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -236,18 +315,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
@@ -270,24 +337,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFEEF1F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
         <bgColor rgb="FFEEF1F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.0499893185216834"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCCF6A"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -414,19 +541,6 @@
         <color rgb="FF9AA3B2"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -526,26 +640,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0"/>
       </left>
@@ -570,6 +664,327 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -585,6 +1000,17 @@
       </right>
       <top style="thin">
         <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -598,298 +1024,911 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -899,7 +1938,154 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF595959"/>
+          <bgColor rgb="FF595959"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7F4F24"/>
+          <bgColor rgb="FF7F4F24"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF57C00"/>
+          <bgColor rgb="FFF57C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -1251,1382 +2437,1358 @@
   <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="15.77734375" customWidth="1" style="70" min="1" max="2"/>
-    <col width="13" customWidth="1" style="70" min="3" max="3"/>
-    <col width="15.77734375" customWidth="1" style="70" min="4" max="4"/>
-    <col width="10" customWidth="1" style="70" min="5" max="5"/>
-    <col width="15.77734375" customWidth="1" style="70" min="6" max="6"/>
-    <col width="11" customWidth="1" style="70" min="7" max="7"/>
-    <col width="15.77734375" customWidth="1" style="70" min="8" max="10"/>
-    <col width="12" customWidth="1" style="70" min="11" max="11"/>
-    <col width="13" customWidth="1" style="70" min="12" max="12"/>
-    <col width="8.88671875" customWidth="1" style="70" min="13" max="16384"/>
+    <col width="15.77734375" customWidth="1" style="127" min="1" max="2"/>
+    <col width="13" customWidth="1" style="127" min="3" max="3"/>
+    <col width="15.77734375" customWidth="1" style="127" min="4" max="10"/>
+    <col width="12" customWidth="1" style="127" min="11" max="11"/>
+    <col width="13" customWidth="1" style="127" min="12" max="12"/>
+    <col width="8.88671875" customWidth="1" style="127" min="13" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="70">
-      <c r="D1" s="35" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="127">
+      <c r="D1" s="133" t="inlineStr">
         <is>
           <t>INSPECCIÓN DE SEGURIDAD</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.4" customHeight="1" s="70">
-      <c r="D2" s="37" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="38" t="n"/>
-    </row>
-    <row r="3" ht="4.95" customHeight="1" s="70">
-      <c r="D3" s="75" t="n"/>
-      <c r="E3" s="56" t="n"/>
-      <c r="F3" s="56" t="n"/>
-      <c r="G3" s="56" t="n"/>
-      <c r="H3" s="56" t="n"/>
-      <c r="I3" s="56" t="n"/>
-      <c r="J3" s="56" t="n"/>
-      <c r="K3" s="56" t="n"/>
-      <c r="L3" s="56" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="70">
-      <c r="J4" s="53" t="inlineStr">
+    <row r="2" ht="14.4" customHeight="1" s="127">
+      <c r="D2" s="96" t="n"/>
+      <c r="E2" s="98" t="n"/>
+      <c r="F2" s="98" t="n"/>
+      <c r="G2" s="98" t="n"/>
+      <c r="H2" s="98" t="n"/>
+      <c r="I2" s="98" t="n"/>
+      <c r="J2" s="98" t="n"/>
+      <c r="K2" s="98" t="n"/>
+      <c r="L2" s="98" t="n"/>
+    </row>
+    <row r="3" ht="4.95" customHeight="1" s="127">
+      <c r="D3" s="60" t="n"/>
+      <c r="E3" s="104" t="n"/>
+      <c r="F3" s="104" t="n"/>
+      <c r="G3" s="104" t="n"/>
+      <c r="H3" s="104" t="n"/>
+      <c r="I3" s="104" t="n"/>
+      <c r="J3" s="104" t="n"/>
+      <c r="K3" s="104" t="n"/>
+      <c r="L3" s="104" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="127">
+      <c r="J4" s="139" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="31" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="70">
-      <c r="D5" s="40" t="inlineStr">
+      <c r="K4" s="93" t="n"/>
+      <c r="L4" s="89" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="127">
+      <c r="D5" s="99" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="I5" s="41" t="n"/>
+      <c r="I5" s="92" t="n"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="K5" s="49" t="inlineStr">
+      <c r="K5" s="64" t="inlineStr">
         <is>
           <t>RYR-SS-010</t>
         </is>
       </c>
-      <c r="L5" s="31" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="70">
-      <c r="D6" s="44" t="inlineStr">
+      <c r="L5" s="89" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="127">
+      <c r="D6" s="90" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN.</t>
         </is>
       </c>
-      <c r="I6" s="41" t="n"/>
+      <c r="I6" s="92" t="n"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="K6" s="49" t="n">
+      <c r="K6" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="31" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="70">
-      <c r="D7" s="109" t="n"/>
-      <c r="E7" s="109" t="n"/>
-      <c r="F7" s="109" t="n"/>
-      <c r="G7" s="109" t="n"/>
-      <c r="H7" s="109" t="n"/>
-      <c r="I7" s="81" t="n"/>
+      <c r="L6" s="89" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="127">
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="67" t="n"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="K7" s="49" t="inlineStr">
+      <c r="K7" s="64" t="inlineStr">
         <is>
           <t>04/10/2026</t>
         </is>
       </c>
-      <c r="L7" s="31" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="70">
-      <c r="D8" s="110" t="n"/>
-      <c r="E8" s="110" t="n"/>
-      <c r="F8" s="110" t="n"/>
-      <c r="G8" s="110" t="n"/>
-      <c r="H8" s="110" t="n"/>
-      <c r="I8" s="81" t="n"/>
+      <c r="L7" s="89" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="127">
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="29" t="n"/>
+      <c r="I8" s="67" t="n"/>
       <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="K8" s="49" t="inlineStr">
+      <c r="K8" s="64" t="inlineStr">
         <is>
           <t>1 de 2</t>
         </is>
       </c>
-      <c r="L8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="70">
-      <c r="A9" s="103" t="inlineStr">
+      <c r="L8" s="89" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="127">
+      <c r="A9" s="142" t="inlineStr">
         <is>
           <t>Inspección planeada de condiciones, equipos y orden en obra · Decreto 1072 de 2015 · Resolución 0312 de 2019</t>
         </is>
       </c>
-      <c r="B9" s="115" t="n"/>
-      <c r="C9" s="115" t="n"/>
-      <c r="D9" s="115" t="n"/>
-      <c r="E9" s="115" t="n"/>
-      <c r="F9" s="115" t="n"/>
-      <c r="G9" s="115" t="n"/>
-      <c r="H9" s="115" t="n"/>
-      <c r="I9" s="115" t="n"/>
-      <c r="J9" s="115" t="n"/>
-      <c r="K9" s="115" t="n"/>
-      <c r="L9" s="116" t="n"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="70">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="B9" s="356" t="n"/>
+      <c r="C9" s="356" t="n"/>
+      <c r="D9" s="356" t="n"/>
+      <c r="E9" s="356" t="n"/>
+      <c r="F9" s="356" t="n"/>
+      <c r="G9" s="356" t="n"/>
+      <c r="H9" s="356" t="n"/>
+      <c r="I9" s="356" t="n"/>
+      <c r="J9" s="356" t="n"/>
+      <c r="K9" s="356" t="n"/>
+      <c r="L9" s="357" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="127">
+      <c r="A10" s="137" t="inlineStr">
         <is>
           <t>1. DATOS DE LA INSPECCIÓN</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="38" t="n"/>
-      <c r="J10" s="38" t="n"/>
-      <c r="K10" s="38" t="n"/>
-      <c r="L10" s="47" t="n"/>
-    </row>
-    <row r="11" ht="21" customHeight="1" s="70">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="B10" s="98" t="n"/>
+      <c r="C10" s="98" t="n"/>
+      <c r="D10" s="98" t="n"/>
+      <c r="E10" s="98" t="n"/>
+      <c r="F10" s="98" t="n"/>
+      <c r="G10" s="98" t="n"/>
+      <c r="H10" s="98" t="n"/>
+      <c r="I10" s="98" t="n"/>
+      <c r="J10" s="98" t="n"/>
+      <c r="K10" s="98" t="n"/>
+      <c r="L10" s="97" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1" s="127">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="50" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="30" t="n"/>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="21" customHeight="1" s="70">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="B11" s="89" t="n"/>
+      <c r="C11" s="161" t="n"/>
+      <c r="D11" s="93" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
+      <c r="G11" s="93" t="n"/>
+      <c r="H11" s="93" t="n"/>
+      <c r="I11" s="93" t="n"/>
+      <c r="J11" s="93" t="n"/>
+      <c r="K11" s="93" t="n"/>
+      <c r="L11" s="89" t="n"/>
+    </row>
+    <row r="12" ht="21" customHeight="1" s="127">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n"/>
-      <c r="C12" s="43" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="33" t="inlineStr">
+      <c r="B12" s="89" t="n"/>
+      <c r="C12" s="68" t="n"/>
+      <c r="D12" s="93" t="n"/>
+      <c r="E12" s="93" t="n"/>
+      <c r="F12" s="93" t="n"/>
+      <c r="G12" s="89" t="n"/>
+      <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="I12" s="31" t="n"/>
-      <c r="J12" s="43" t="n"/>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="21" customHeight="1" s="70">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="I12" s="89" t="n"/>
+      <c r="J12" s="68" t="n"/>
+      <c r="K12" s="93" t="n"/>
+      <c r="L12" s="89" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1" s="127">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>Fecha de la inspección</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="48" t="n"/>
-      <c r="D13" s="33" t="inlineStr">
+      <c r="B13" s="89" t="n"/>
+      <c r="C13" s="69" t="n"/>
+      <c r="D13" s="59" t="inlineStr">
         <is>
           <t>Hora inicio</t>
         </is>
       </c>
-      <c r="E13" s="48" t="n"/>
-      <c r="F13" s="33" t="inlineStr">
+      <c r="E13" s="69" t="n"/>
+      <c r="F13" s="59" t="inlineStr">
         <is>
           <t>Hora fin</t>
         </is>
       </c>
-      <c r="G13" s="48" t="n"/>
-      <c r="H13" s="33" t="inlineStr">
+      <c r="G13" s="69" t="n"/>
+      <c r="H13" s="59" t="inlineStr">
         <is>
           <t>Duración</t>
         </is>
       </c>
-      <c r="I13" s="48">
+      <c r="I13" s="69">
         <f>IFERROR(IF(OR(E13="",G13=""),"",TEXT(G13-E13,"h:mm")),"")</f>
         <v/>
       </c>
-      <c r="J13" s="33" t="inlineStr">
+      <c r="J13" s="59" t="inlineStr">
         <is>
           <t>N° de inspección</t>
         </is>
       </c>
-      <c r="K13" s="48" t="n"/>
-      <c r="L13" s="31" t="n"/>
-    </row>
-    <row r="14" ht="21" customHeight="1" s="70">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="K13" s="69" t="n"/>
+      <c r="L13" s="89" t="n"/>
+    </row>
+    <row r="14" ht="21" customHeight="1" s="127">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>Tipo de inspección</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="43" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="31" t="n"/>
-      <c r="H14" s="33" t="inlineStr">
+      <c r="B14" s="89" t="n"/>
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="93" t="n"/>
+      <c r="E14" s="93" t="n"/>
+      <c r="F14" s="93" t="n"/>
+      <c r="G14" s="89" t="n"/>
+      <c r="H14" s="59" t="inlineStr">
         <is>
           <t>Área / frente inspeccionado</t>
         </is>
       </c>
-      <c r="I14" s="31" t="n"/>
-      <c r="J14" s="43" t="n"/>
-      <c r="K14" s="30" t="n"/>
-      <c r="L14" s="31" t="n"/>
-    </row>
-    <row r="15" ht="21" customHeight="1" s="70">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="I14" s="89" t="n"/>
+      <c r="J14" s="68" t="n"/>
+      <c r="K14" s="93" t="n"/>
+      <c r="L14" s="89" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" s="127">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="43" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="33" t="inlineStr">
+      <c r="B15" s="89" t="n"/>
+      <c r="C15" s="68" t="n"/>
+      <c r="D15" s="93" t="n"/>
+      <c r="E15" s="93" t="n"/>
+      <c r="F15" s="93" t="n"/>
+      <c r="G15" s="89" t="n"/>
+      <c r="H15" s="59" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="I15" s="31" t="n"/>
-      <c r="J15" s="43" t="n"/>
-      <c r="K15" s="30" t="n"/>
-      <c r="L15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="21" customHeight="1" s="70">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="I15" s="89" t="n"/>
+      <c r="J15" s="68" t="n"/>
+      <c r="K15" s="93" t="n"/>
+      <c r="L15" s="89" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1" s="127">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>Acompaña (responsable del área)</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="43" t="n"/>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="31" t="n"/>
-      <c r="H16" s="33" t="inlineStr">
+      <c r="B16" s="89" t="n"/>
+      <c r="C16" s="68" t="n"/>
+      <c r="D16" s="93" t="n"/>
+      <c r="E16" s="93" t="n"/>
+      <c r="F16" s="93" t="n"/>
+      <c r="G16" s="89" t="n"/>
+      <c r="H16" s="59" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="I16" s="31" t="n"/>
-      <c r="J16" s="43" t="n"/>
-      <c r="K16" s="30" t="n"/>
-      <c r="L16" s="31" t="n"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" s="70">
-      <c r="A17" s="54" t="inlineStr">
+      <c r="I16" s="89" t="n"/>
+      <c r="J16" s="68" t="n"/>
+      <c r="K16" s="93" t="n"/>
+      <c r="L16" s="89" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="127">
+      <c r="A17" s="227" t="inlineStr">
         <is>
           <t>2. LISTA DE VERIFICACIÓN (marque con X la casilla que corresponda)</t>
         </is>
       </c>
-      <c r="B17" s="38" t="n"/>
-      <c r="C17" s="38" t="n"/>
-      <c r="D17" s="38" t="n"/>
-      <c r="E17" s="38" t="n"/>
-      <c r="F17" s="38" t="n"/>
-      <c r="G17" s="38" t="n"/>
-      <c r="H17" s="38" t="n"/>
-      <c r="I17" s="38" t="n"/>
-      <c r="J17" s="38" t="n"/>
-      <c r="K17" s="38" t="n"/>
-      <c r="L17" s="47" t="n"/>
-    </row>
-    <row r="18" ht="19.05" customHeight="1" s="70">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="L17" s="92" t="n"/>
+    </row>
+    <row r="18" ht="19.05" customHeight="1" s="127">
+      <c r="A18" s="259" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="259" t="inlineStr">
         <is>
           <t>Aspecto verificado</t>
         </is>
       </c>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="31" t="n"/>
-      <c r="H18" s="34" t="inlineStr">
+      <c r="C18" s="347" t="n"/>
+      <c r="D18" s="347" t="n"/>
+      <c r="E18" s="347" t="n"/>
+      <c r="F18" s="347" t="n"/>
+      <c r="G18" s="348" t="n"/>
+      <c r="H18" s="259" t="inlineStr">
         <is>
           <t>Cumple</t>
         </is>
       </c>
-      <c r="I18" s="34" t="inlineStr">
+      <c r="I18" s="259" t="inlineStr">
         <is>
           <t>No cumple</t>
         </is>
       </c>
-      <c r="J18" s="34" t="inlineStr">
+      <c r="J18" s="259" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K18" s="34" t="inlineStr">
+      <c r="K18" s="259" t="inlineStr">
         <is>
           <t>Observación / hallazgo</t>
         </is>
       </c>
-      <c r="L18" s="31" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="70">
-      <c r="A19" s="88" t="inlineStr">
+      <c r="L18" s="348" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="127">
+      <c r="A19" s="307" t="inlineStr">
         <is>
           <t>A. ORDEN Y ASEO</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="30" t="n"/>
-      <c r="H19" s="30" t="n"/>
-      <c r="I19" s="30" t="n"/>
-      <c r="J19" s="30" t="n"/>
-      <c r="K19" s="30" t="n"/>
-      <c r="L19" s="31" t="n"/>
-    </row>
-    <row r="20" ht="16.95" customHeight="1" s="70">
-      <c r="A20" s="57" t="n">
+      <c r="B19" s="98" t="n"/>
+      <c r="C19" s="98" t="n"/>
+      <c r="D19" s="98" t="n"/>
+      <c r="E19" s="98" t="n"/>
+      <c r="F19" s="98" t="n"/>
+      <c r="G19" s="98" t="n"/>
+      <c r="H19" s="98" t="n"/>
+      <c r="I19" s="98" t="n"/>
+      <c r="J19" s="98" t="n"/>
+      <c r="K19" s="98" t="n"/>
+      <c r="L19" s="97" t="n"/>
+    </row>
+    <row r="20" ht="16.95" customHeight="1" s="127">
+      <c r="A20" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="89" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>Áreas de trabajo y de circulación despejadas</t>
         </is>
       </c>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="30" t="n"/>
-      <c r="G20" s="31" t="n"/>
-      <c r="H20" s="57" t="n"/>
-      <c r="I20" s="57" t="n"/>
-      <c r="J20" s="57" t="n"/>
-      <c r="K20" s="29" t="n"/>
-      <c r="L20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="16.95" customHeight="1" s="70">
-      <c r="A21" s="57" t="n">
+      <c r="C20" s="93" t="n"/>
+      <c r="D20" s="93" t="n"/>
+      <c r="E20" s="93" t="n"/>
+      <c r="F20" s="93" t="n"/>
+      <c r="G20" s="89" t="n"/>
+      <c r="H20" s="126" t="n"/>
+      <c r="I20" s="126" t="n"/>
+      <c r="J20" s="126" t="n"/>
+      <c r="K20" s="76" t="n"/>
+      <c r="L20" s="89" t="n"/>
+    </row>
+    <row r="21" ht="16.95" customHeight="1" s="127">
+      <c r="A21" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="89" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Materiales apilados y almacenados de forma segura</t>
         </is>
       </c>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="31" t="n"/>
-      <c r="H21" s="57" t="n"/>
-      <c r="I21" s="57" t="n"/>
-      <c r="J21" s="57" t="n"/>
-      <c r="K21" s="29" t="n"/>
-      <c r="L21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="16.95" customHeight="1" s="70">
-      <c r="A22" s="57" t="n">
+      <c r="C21" s="93" t="n"/>
+      <c r="D21" s="93" t="n"/>
+      <c r="E21" s="93" t="n"/>
+      <c r="F21" s="93" t="n"/>
+      <c r="G21" s="89" t="n"/>
+      <c r="H21" s="126" t="n"/>
+      <c r="I21" s="126" t="n"/>
+      <c r="J21" s="126" t="n"/>
+      <c r="K21" s="76" t="n"/>
+      <c r="L21" s="89" t="n"/>
+    </row>
+    <row r="22" ht="16.95" customHeight="1" s="127">
+      <c r="A22" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="89" t="inlineStr">
+      <c r="B22" s="72" t="inlineStr">
         <is>
           <t>Residuos clasificados y recipientes disponibles</t>
         </is>
       </c>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="30" t="n"/>
-      <c r="G22" s="31" t="n"/>
-      <c r="H22" s="57" t="n"/>
-      <c r="I22" s="57" t="n"/>
-      <c r="J22" s="57" t="n"/>
-      <c r="K22" s="29" t="n"/>
-      <c r="L22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="16.95" customHeight="1" s="70">
-      <c r="A23" s="57" t="n">
+      <c r="C22" s="93" t="n"/>
+      <c r="D22" s="93" t="n"/>
+      <c r="E22" s="93" t="n"/>
+      <c r="F22" s="93" t="n"/>
+      <c r="G22" s="89" t="n"/>
+      <c r="H22" s="126" t="n"/>
+      <c r="I22" s="126" t="n"/>
+      <c r="J22" s="126" t="n"/>
+      <c r="K22" s="76" t="n"/>
+      <c r="L22" s="89" t="n"/>
+    </row>
+    <row r="23" ht="16.95" customHeight="1" s="127">
+      <c r="A23" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="89" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>Baños, comedor y campamento en condiciones de higiene</t>
         </is>
       </c>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="31" t="n"/>
-      <c r="H23" s="57" t="n"/>
-      <c r="I23" s="57" t="n"/>
-      <c r="J23" s="57" t="n"/>
-      <c r="K23" s="29" t="n"/>
-      <c r="L23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="70">
-      <c r="A24" s="88" t="inlineStr">
+      <c r="C23" s="93" t="n"/>
+      <c r="D23" s="93" t="n"/>
+      <c r="E23" s="93" t="n"/>
+      <c r="F23" s="93" t="n"/>
+      <c r="G23" s="89" t="n"/>
+      <c r="H23" s="126" t="n"/>
+      <c r="I23" s="126" t="n"/>
+      <c r="J23" s="126" t="n"/>
+      <c r="K23" s="76" t="n"/>
+      <c r="L23" s="89" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="127">
+      <c r="A24" s="162" t="inlineStr">
         <is>
           <t>B. SEÑALIZACIÓN Y DEMARCACIÓN</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="30" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="30" t="n"/>
-      <c r="I24" s="30" t="n"/>
-      <c r="J24" s="30" t="n"/>
-      <c r="K24" s="30" t="n"/>
-      <c r="L24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="16.95" customHeight="1" s="70">
-      <c r="A25" s="57" t="n">
+      <c r="B24" s="93" t="n"/>
+      <c r="C24" s="93" t="n"/>
+      <c r="D24" s="93" t="n"/>
+      <c r="E24" s="93" t="n"/>
+      <c r="F24" s="93" t="n"/>
+      <c r="G24" s="93" t="n"/>
+      <c r="H24" s="93" t="n"/>
+      <c r="I24" s="93" t="n"/>
+      <c r="J24" s="93" t="n"/>
+      <c r="K24" s="93" t="n"/>
+      <c r="L24" s="89" t="n"/>
+    </row>
+    <row r="25" ht="16.95" customHeight="1" s="127">
+      <c r="A25" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="89" t="inlineStr">
+      <c r="B25" s="72" t="inlineStr">
         <is>
           <t>Señalización de seguridad visible y completa</t>
         </is>
       </c>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="30" t="n"/>
-      <c r="G25" s="31" t="n"/>
-      <c r="H25" s="57" t="n"/>
-      <c r="I25" s="57" t="n"/>
-      <c r="J25" s="57" t="n"/>
-      <c r="K25" s="29" t="n"/>
-      <c r="L25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="16.95" customHeight="1" s="70">
-      <c r="A26" s="57" t="n">
+      <c r="C25" s="93" t="n"/>
+      <c r="D25" s="93" t="n"/>
+      <c r="E25" s="93" t="n"/>
+      <c r="F25" s="93" t="n"/>
+      <c r="G25" s="89" t="n"/>
+      <c r="H25" s="126" t="n"/>
+      <c r="I25" s="126" t="n"/>
+      <c r="J25" s="126" t="n"/>
+      <c r="K25" s="76" t="n"/>
+      <c r="L25" s="89" t="n"/>
+    </row>
+    <row r="26" ht="16.95" customHeight="1" s="127">
+      <c r="A26" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="89" t="inlineStr">
+      <c r="B26" s="72" t="inlineStr">
         <is>
           <t>Áreas de riesgo demarcadas y cerradas</t>
         </is>
       </c>
-      <c r="C26" s="30" t="n"/>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="30" t="n"/>
-      <c r="F26" s="30" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="57" t="n"/>
-      <c r="I26" s="57" t="n"/>
-      <c r="J26" s="57" t="n"/>
-      <c r="K26" s="29" t="n"/>
-      <c r="L26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="16.95" customHeight="1" s="70">
-      <c r="A27" s="57" t="n">
+      <c r="C26" s="93" t="n"/>
+      <c r="D26" s="93" t="n"/>
+      <c r="E26" s="93" t="n"/>
+      <c r="F26" s="93" t="n"/>
+      <c r="G26" s="89" t="n"/>
+      <c r="H26" s="126" t="n"/>
+      <c r="I26" s="126" t="n"/>
+      <c r="J26" s="126" t="n"/>
+      <c r="K26" s="76" t="n"/>
+      <c r="L26" s="89" t="n"/>
+    </row>
+    <row r="27" ht="16.95" customHeight="1" s="127">
+      <c r="A27" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B27" s="89" t="inlineStr">
+      <c r="B27" s="72" t="inlineStr">
         <is>
           <t>Rutas de evacuación y puntos de encuentro señalizados</t>
         </is>
       </c>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="30" t="n"/>
-      <c r="G27" s="31" t="n"/>
-      <c r="H27" s="57" t="n"/>
-      <c r="I27" s="57" t="n"/>
-      <c r="J27" s="57" t="n"/>
-      <c r="K27" s="29" t="n"/>
-      <c r="L27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="70">
-      <c r="A28" s="88" t="inlineStr">
+      <c r="C27" s="93" t="n"/>
+      <c r="D27" s="93" t="n"/>
+      <c r="E27" s="93" t="n"/>
+      <c r="F27" s="93" t="n"/>
+      <c r="G27" s="89" t="n"/>
+      <c r="H27" s="126" t="n"/>
+      <c r="I27" s="126" t="n"/>
+      <c r="J27" s="126" t="n"/>
+      <c r="K27" s="76" t="n"/>
+      <c r="L27" s="89" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="127">
+      <c r="A28" s="162" t="inlineStr">
         <is>
           <t>C. HERRAMIENTAS Y EQUIPOS</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="30" t="n"/>
-      <c r="F28" s="30" t="n"/>
-      <c r="G28" s="30" t="n"/>
-      <c r="H28" s="30" t="n"/>
-      <c r="I28" s="30" t="n"/>
-      <c r="J28" s="30" t="n"/>
-      <c r="K28" s="30" t="n"/>
-      <c r="L28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="16.95" customHeight="1" s="70">
-      <c r="A29" s="57" t="n">
+      <c r="B28" s="93" t="n"/>
+      <c r="C28" s="93" t="n"/>
+      <c r="D28" s="93" t="n"/>
+      <c r="E28" s="93" t="n"/>
+      <c r="F28" s="93" t="n"/>
+      <c r="G28" s="93" t="n"/>
+      <c r="H28" s="93" t="n"/>
+      <c r="I28" s="93" t="n"/>
+      <c r="J28" s="93" t="n"/>
+      <c r="K28" s="93" t="n"/>
+      <c r="L28" s="89" t="n"/>
+    </row>
+    <row r="29" ht="16.95" customHeight="1" s="127">
+      <c r="A29" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="89" t="inlineStr">
+      <c r="B29" s="72" t="inlineStr">
         <is>
           <t>Herramientas manuales en buen estado y bien almacenadas</t>
         </is>
       </c>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="31" t="n"/>
-      <c r="H29" s="57" t="n"/>
-      <c r="I29" s="57" t="n"/>
-      <c r="J29" s="57" t="n"/>
-      <c r="K29" s="29" t="n"/>
-      <c r="L29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="16.95" customHeight="1" s="70">
-      <c r="A30" s="57" t="n">
+      <c r="C29" s="93" t="n"/>
+      <c r="D29" s="93" t="n"/>
+      <c r="E29" s="93" t="n"/>
+      <c r="F29" s="93" t="n"/>
+      <c r="G29" s="89" t="n"/>
+      <c r="H29" s="126" t="n"/>
+      <c r="I29" s="126" t="n"/>
+      <c r="J29" s="126" t="n"/>
+      <c r="K29" s="76" t="n"/>
+      <c r="L29" s="89" t="n"/>
+    </row>
+    <row r="30" ht="16.95" customHeight="1" s="127">
+      <c r="A30" s="126" t="n">
         <v>9</v>
       </c>
-      <c r="B30" s="89" t="inlineStr">
+      <c r="B30" s="72" t="inlineStr">
         <is>
           <t>Equipos eléctricos con guardas y cables en buen estado</t>
         </is>
       </c>
-      <c r="C30" s="30" t="n"/>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="30" t="n"/>
-      <c r="F30" s="30" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="57" t="n"/>
-      <c r="I30" s="57" t="n"/>
-      <c r="J30" s="57" t="n"/>
-      <c r="K30" s="29" t="n"/>
-      <c r="L30" s="31" t="n"/>
-    </row>
-    <row r="31" ht="16.95" customHeight="1" s="70">
-      <c r="A31" s="57" t="n">
+      <c r="C30" s="93" t="n"/>
+      <c r="D30" s="93" t="n"/>
+      <c r="E30" s="93" t="n"/>
+      <c r="F30" s="93" t="n"/>
+      <c r="G30" s="89" t="n"/>
+      <c r="H30" s="126" t="n"/>
+      <c r="I30" s="126" t="n"/>
+      <c r="J30" s="126" t="n"/>
+      <c r="K30" s="76" t="n"/>
+      <c r="L30" s="89" t="n"/>
+    </row>
+    <row r="31" ht="16.95" customHeight="1" s="127">
+      <c r="A31" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="89" t="inlineStr">
+      <c r="B31" s="72" t="inlineStr">
         <is>
           <t>Maquinaria con inspección preoperacional al día</t>
         </is>
       </c>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="30" t="n"/>
-      <c r="F31" s="30" t="n"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="57" t="n"/>
-      <c r="I31" s="57" t="n"/>
-      <c r="J31" s="57" t="n"/>
-      <c r="K31" s="29" t="n"/>
-      <c r="L31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="16.95" customHeight="1" s="70">
-      <c r="A32" s="57" t="n">
+      <c r="C31" s="93" t="n"/>
+      <c r="D31" s="93" t="n"/>
+      <c r="E31" s="93" t="n"/>
+      <c r="F31" s="93" t="n"/>
+      <c r="G31" s="89" t="n"/>
+      <c r="H31" s="126" t="n"/>
+      <c r="I31" s="126" t="n"/>
+      <c r="J31" s="126" t="n"/>
+      <c r="K31" s="76" t="n"/>
+      <c r="L31" s="89" t="n"/>
+    </row>
+    <row r="32" ht="16.95" customHeight="1" s="127">
+      <c r="A32" s="126" t="n">
         <v>11</v>
       </c>
-      <c r="B32" s="89" t="inlineStr">
+      <c r="B32" s="72" t="inlineStr">
         <is>
           <t>Equipos de izaje y accesorios certificados</t>
         </is>
       </c>
-      <c r="C32" s="30" t="n"/>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="30" t="n"/>
-      <c r="F32" s="30" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="57" t="n"/>
-      <c r="I32" s="57" t="n"/>
-      <c r="J32" s="57" t="n"/>
-      <c r="K32" s="29" t="n"/>
-      <c r="L32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="70">
-      <c r="A33" s="88" t="inlineStr">
+      <c r="C32" s="93" t="n"/>
+      <c r="D32" s="93" t="n"/>
+      <c r="E32" s="93" t="n"/>
+      <c r="F32" s="93" t="n"/>
+      <c r="G32" s="89" t="n"/>
+      <c r="H32" s="126" t="n"/>
+      <c r="I32" s="126" t="n"/>
+      <c r="J32" s="126" t="n"/>
+      <c r="K32" s="76" t="n"/>
+      <c r="L32" s="89" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="127">
+      <c r="A33" s="162" t="inlineStr">
         <is>
           <t>D. INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="30" t="n"/>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="30" t="n"/>
-      <c r="H33" s="30" t="n"/>
-      <c r="I33" s="30" t="n"/>
-      <c r="J33" s="30" t="n"/>
-      <c r="K33" s="30" t="n"/>
-      <c r="L33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="16.95" customHeight="1" s="70">
-      <c r="A34" s="57" t="n">
+      <c r="B33" s="93" t="n"/>
+      <c r="C33" s="93" t="n"/>
+      <c r="D33" s="93" t="n"/>
+      <c r="E33" s="93" t="n"/>
+      <c r="F33" s="93" t="n"/>
+      <c r="G33" s="93" t="n"/>
+      <c r="H33" s="93" t="n"/>
+      <c r="I33" s="93" t="n"/>
+      <c r="J33" s="93" t="n"/>
+      <c r="K33" s="93" t="n"/>
+      <c r="L33" s="89" t="n"/>
+    </row>
+    <row r="34" ht="16.95" customHeight="1" s="127">
+      <c r="A34" s="126" t="n">
         <v>12</v>
       </c>
-      <c r="B34" s="89" t="inlineStr">
+      <c r="B34" s="72" t="inlineStr">
         <is>
           <t>Tableros cerrados, rotulados y con protección</t>
         </is>
       </c>
-      <c r="C34" s="30" t="n"/>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="30" t="n"/>
-      <c r="F34" s="30" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="57" t="n"/>
-      <c r="I34" s="57" t="n"/>
-      <c r="J34" s="57" t="n"/>
-      <c r="K34" s="29" t="n"/>
-      <c r="L34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="16.95" customHeight="1" s="70">
-      <c r="A35" s="57" t="n">
+      <c r="C34" s="93" t="n"/>
+      <c r="D34" s="93" t="n"/>
+      <c r="E34" s="93" t="n"/>
+      <c r="F34" s="93" t="n"/>
+      <c r="G34" s="89" t="n"/>
+      <c r="H34" s="126" t="n"/>
+      <c r="I34" s="126" t="n"/>
+      <c r="J34" s="126" t="n"/>
+      <c r="K34" s="76" t="n"/>
+      <c r="L34" s="89" t="n"/>
+    </row>
+    <row r="35" ht="16.95" customHeight="1" s="127">
+      <c r="A35" s="126" t="n">
         <v>13</v>
       </c>
-      <c r="B35" s="89" t="inlineStr">
+      <c r="B35" s="72" t="inlineStr">
         <is>
           <t>Extensiones y empalmes en buen estado (sin cables pelados)</t>
         </is>
       </c>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="30" t="n"/>
-      <c r="F35" s="30" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="57" t="n"/>
-      <c r="I35" s="57" t="n"/>
-      <c r="J35" s="57" t="n"/>
-      <c r="K35" s="29" t="n"/>
-      <c r="L35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="16.95" customHeight="1" s="70">
-      <c r="A36" s="57" t="n">
+      <c r="C35" s="93" t="n"/>
+      <c r="D35" s="93" t="n"/>
+      <c r="E35" s="93" t="n"/>
+      <c r="F35" s="93" t="n"/>
+      <c r="G35" s="89" t="n"/>
+      <c r="H35" s="126" t="n"/>
+      <c r="I35" s="126" t="n"/>
+      <c r="J35" s="126" t="n"/>
+      <c r="K35" s="76" t="n"/>
+      <c r="L35" s="89" t="n"/>
+    </row>
+    <row r="36" ht="16.95" customHeight="1" s="127">
+      <c r="A36" s="126" t="n">
         <v>14</v>
       </c>
-      <c r="B36" s="89" t="inlineStr">
+      <c r="B36" s="72" t="inlineStr">
         <is>
           <t>Conexión a tierra y protección diferencial</t>
         </is>
       </c>
-      <c r="C36" s="30" t="n"/>
-      <c r="D36" s="30" t="n"/>
-      <c r="E36" s="30" t="n"/>
-      <c r="F36" s="30" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="57" t="n"/>
-      <c r="I36" s="57" t="n"/>
-      <c r="J36" s="57" t="n"/>
-      <c r="K36" s="29" t="n"/>
-      <c r="L36" s="31" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="70">
-      <c r="A37" s="88" t="inlineStr">
+      <c r="C36" s="93" t="n"/>
+      <c r="D36" s="93" t="n"/>
+      <c r="E36" s="93" t="n"/>
+      <c r="F36" s="93" t="n"/>
+      <c r="G36" s="89" t="n"/>
+      <c r="H36" s="126" t="n"/>
+      <c r="I36" s="126" t="n"/>
+      <c r="J36" s="126" t="n"/>
+      <c r="K36" s="76" t="n"/>
+      <c r="L36" s="89" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="127">
+      <c r="A37" s="162" t="inlineStr">
         <is>
           <t>E. TRABAJO EN ALTURAS</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="30" t="n"/>
-      <c r="F37" s="30" t="n"/>
-      <c r="G37" s="30" t="n"/>
-      <c r="H37" s="30" t="n"/>
-      <c r="I37" s="30" t="n"/>
-      <c r="J37" s="30" t="n"/>
-      <c r="K37" s="30" t="n"/>
-      <c r="L37" s="31" t="n"/>
-    </row>
-    <row r="38" ht="16.95" customHeight="1" s="70">
-      <c r="A38" s="57" t="n">
+      <c r="B37" s="93" t="n"/>
+      <c r="C37" s="93" t="n"/>
+      <c r="D37" s="93" t="n"/>
+      <c r="E37" s="93" t="n"/>
+      <c r="F37" s="93" t="n"/>
+      <c r="G37" s="93" t="n"/>
+      <c r="H37" s="93" t="n"/>
+      <c r="I37" s="93" t="n"/>
+      <c r="J37" s="93" t="n"/>
+      <c r="K37" s="93" t="n"/>
+      <c r="L37" s="89" t="n"/>
+    </row>
+    <row r="38" ht="16.95" customHeight="1" s="127">
+      <c r="A38" s="126" t="n">
         <v>15</v>
       </c>
-      <c r="B38" s="89" t="inlineStr">
+      <c r="B38" s="72" t="inlineStr">
         <is>
           <t>Andamios armados, certificados y con tarjeta de inspección</t>
         </is>
       </c>
-      <c r="C38" s="30" t="n"/>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="30" t="n"/>
-      <c r="F38" s="30" t="n"/>
-      <c r="G38" s="31" t="n"/>
-      <c r="H38" s="57" t="n"/>
-      <c r="I38" s="57" t="n"/>
-      <c r="J38" s="57" t="n"/>
-      <c r="K38" s="29" t="n"/>
-      <c r="L38" s="31" t="n"/>
-    </row>
-    <row r="39" ht="16.95" customHeight="1" s="70">
-      <c r="A39" s="57" t="n">
+      <c r="C38" s="93" t="n"/>
+      <c r="D38" s="93" t="n"/>
+      <c r="E38" s="93" t="n"/>
+      <c r="F38" s="93" t="n"/>
+      <c r="G38" s="89" t="n"/>
+      <c r="H38" s="126" t="n"/>
+      <c r="I38" s="126" t="n"/>
+      <c r="J38" s="126" t="n"/>
+      <c r="K38" s="76" t="n"/>
+      <c r="L38" s="89" t="n"/>
+    </row>
+    <row r="39" ht="16.95" customHeight="1" s="127">
+      <c r="A39" s="126" t="n">
         <v>16</v>
       </c>
-      <c r="B39" s="89" t="inlineStr">
+      <c r="B39" s="72" t="inlineStr">
         <is>
           <t>Escaleras en buen estado y bien utilizadas</t>
         </is>
       </c>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="30" t="n"/>
-      <c r="F39" s="30" t="n"/>
-      <c r="G39" s="31" t="n"/>
-      <c r="H39" s="57" t="n"/>
-      <c r="I39" s="57" t="n"/>
-      <c r="J39" s="57" t="n"/>
-      <c r="K39" s="29" t="n"/>
-      <c r="L39" s="31" t="n"/>
-    </row>
-    <row r="40" ht="16.95" customHeight="1" s="70">
-      <c r="A40" s="57" t="n">
+      <c r="C39" s="93" t="n"/>
+      <c r="D39" s="93" t="n"/>
+      <c r="E39" s="93" t="n"/>
+      <c r="F39" s="93" t="n"/>
+      <c r="G39" s="89" t="n"/>
+      <c r="H39" s="126" t="n"/>
+      <c r="I39" s="126" t="n"/>
+      <c r="J39" s="126" t="n"/>
+      <c r="K39" s="76" t="n"/>
+      <c r="L39" s="89" t="n"/>
+    </row>
+    <row r="40" ht="16.95" customHeight="1" s="127">
+      <c r="A40" s="126" t="n">
         <v>17</v>
       </c>
-      <c r="B40" s="89" t="inlineStr">
+      <c r="B40" s="72" t="inlineStr">
         <is>
           <t>Puntos de anclaje, líneas de vida y arneses inspeccionados</t>
         </is>
       </c>
-      <c r="C40" s="30" t="n"/>
-      <c r="D40" s="30" t="n"/>
-      <c r="E40" s="30" t="n"/>
-      <c r="F40" s="30" t="n"/>
-      <c r="G40" s="31" t="n"/>
-      <c r="H40" s="57" t="n"/>
-      <c r="I40" s="57" t="n"/>
-      <c r="J40" s="57" t="n"/>
-      <c r="K40" s="29" t="n"/>
-      <c r="L40" s="31" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="70">
-      <c r="A41" s="88" t="inlineStr">
+      <c r="C40" s="93" t="n"/>
+      <c r="D40" s="93" t="n"/>
+      <c r="E40" s="93" t="n"/>
+      <c r="F40" s="93" t="n"/>
+      <c r="G40" s="89" t="n"/>
+      <c r="H40" s="126" t="n"/>
+      <c r="I40" s="126" t="n"/>
+      <c r="J40" s="126" t="n"/>
+      <c r="K40" s="76" t="n"/>
+      <c r="L40" s="89" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="127">
+      <c r="A41" s="162" t="inlineStr">
         <is>
           <t>F. EMERGENCIAS</t>
         </is>
       </c>
-      <c r="B41" s="30" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="30" t="n"/>
-      <c r="F41" s="30" t="n"/>
-      <c r="G41" s="30" t="n"/>
-      <c r="H41" s="30" t="n"/>
-      <c r="I41" s="30" t="n"/>
-      <c r="J41" s="30" t="n"/>
-      <c r="K41" s="30" t="n"/>
-      <c r="L41" s="31" t="n"/>
-    </row>
-    <row r="42" ht="16.95" customHeight="1" s="70">
-      <c r="A42" s="57" t="n">
+      <c r="B41" s="93" t="n"/>
+      <c r="C41" s="93" t="n"/>
+      <c r="D41" s="93" t="n"/>
+      <c r="E41" s="93" t="n"/>
+      <c r="F41" s="93" t="n"/>
+      <c r="G41" s="93" t="n"/>
+      <c r="H41" s="93" t="n"/>
+      <c r="I41" s="93" t="n"/>
+      <c r="J41" s="93" t="n"/>
+      <c r="K41" s="93" t="n"/>
+      <c r="L41" s="89" t="n"/>
+    </row>
+    <row r="42" ht="16.95" customHeight="1" s="127">
+      <c r="A42" s="126" t="n">
         <v>18</v>
       </c>
-      <c r="B42" s="89" t="inlineStr">
+      <c r="B42" s="72" t="inlineStr">
         <is>
           <t>Extintores vigentes, señalizados y accesibles</t>
         </is>
       </c>
-      <c r="C42" s="30" t="n"/>
-      <c r="D42" s="30" t="n"/>
-      <c r="E42" s="30" t="n"/>
-      <c r="F42" s="30" t="n"/>
-      <c r="G42" s="31" t="n"/>
-      <c r="H42" s="57" t="n"/>
-      <c r="I42" s="57" t="n"/>
-      <c r="J42" s="57" t="n"/>
-      <c r="K42" s="29" t="n"/>
-      <c r="L42" s="31" t="n"/>
-    </row>
-    <row r="43" ht="16.95" customHeight="1" s="70">
-      <c r="A43" s="57" t="n">
+      <c r="C42" s="93" t="n"/>
+      <c r="D42" s="93" t="n"/>
+      <c r="E42" s="93" t="n"/>
+      <c r="F42" s="93" t="n"/>
+      <c r="G42" s="89" t="n"/>
+      <c r="H42" s="126" t="n"/>
+      <c r="I42" s="126" t="n"/>
+      <c r="J42" s="126" t="n"/>
+      <c r="K42" s="76" t="n"/>
+      <c r="L42" s="89" t="n"/>
+    </row>
+    <row r="43" ht="16.95" customHeight="1" s="127">
+      <c r="A43" s="126" t="n">
         <v>19</v>
       </c>
-      <c r="B43" s="89" t="inlineStr">
+      <c r="B43" s="72" t="inlineStr">
         <is>
           <t>Botiquín dotado y camilla disponible</t>
         </is>
       </c>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="30" t="n"/>
-      <c r="E43" s="30" t="n"/>
-      <c r="F43" s="30" t="n"/>
-      <c r="G43" s="31" t="n"/>
-      <c r="H43" s="57" t="n"/>
-      <c r="I43" s="57" t="n"/>
-      <c r="J43" s="57" t="n"/>
-      <c r="K43" s="29" t="n"/>
-      <c r="L43" s="31" t="n"/>
-    </row>
-    <row r="44" ht="16.95" customHeight="1" s="70">
-      <c r="A44" s="57" t="n">
+      <c r="C43" s="93" t="n"/>
+      <c r="D43" s="93" t="n"/>
+      <c r="E43" s="93" t="n"/>
+      <c r="F43" s="93" t="n"/>
+      <c r="G43" s="89" t="n"/>
+      <c r="H43" s="126" t="n"/>
+      <c r="I43" s="126" t="n"/>
+      <c r="J43" s="126" t="n"/>
+      <c r="K43" s="76" t="n"/>
+      <c r="L43" s="89" t="n"/>
+    </row>
+    <row r="44" ht="16.95" customHeight="1" s="127">
+      <c r="A44" s="126" t="n">
         <v>20</v>
       </c>
-      <c r="B44" s="89" t="inlineStr">
+      <c r="B44" s="72" t="inlineStr">
         <is>
           <t>Directorio de emergencias visible y brigada conformada</t>
         </is>
       </c>
-      <c r="C44" s="30" t="n"/>
-      <c r="D44" s="30" t="n"/>
-      <c r="E44" s="30" t="n"/>
-      <c r="F44" s="30" t="n"/>
-      <c r="G44" s="31" t="n"/>
-      <c r="H44" s="57" t="n"/>
-      <c r="I44" s="57" t="n"/>
-      <c r="J44" s="57" t="n"/>
-      <c r="K44" s="29" t="n"/>
-      <c r="L44" s="31" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="70">
-      <c r="A45" s="88" t="inlineStr">
+      <c r="C44" s="93" t="n"/>
+      <c r="D44" s="93" t="n"/>
+      <c r="E44" s="93" t="n"/>
+      <c r="F44" s="93" t="n"/>
+      <c r="G44" s="89" t="n"/>
+      <c r="H44" s="126" t="n"/>
+      <c r="I44" s="126" t="n"/>
+      <c r="J44" s="126" t="n"/>
+      <c r="K44" s="76" t="n"/>
+      <c r="L44" s="89" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="127">
+      <c r="A45" s="162" t="inlineStr">
         <is>
           <t>G. PERSONAL Y EPP</t>
         </is>
       </c>
-      <c r="B45" s="30" t="n"/>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="30" t="n"/>
-      <c r="E45" s="30" t="n"/>
-      <c r="F45" s="30" t="n"/>
-      <c r="G45" s="30" t="n"/>
-      <c r="H45" s="30" t="n"/>
-      <c r="I45" s="30" t="n"/>
-      <c r="J45" s="30" t="n"/>
-      <c r="K45" s="30" t="n"/>
-      <c r="L45" s="31" t="n"/>
-    </row>
-    <row r="46" ht="16.95" customHeight="1" s="70">
-      <c r="A46" s="57" t="n">
+      <c r="B45" s="93" t="n"/>
+      <c r="C45" s="93" t="n"/>
+      <c r="D45" s="93" t="n"/>
+      <c r="E45" s="93" t="n"/>
+      <c r="F45" s="93" t="n"/>
+      <c r="G45" s="93" t="n"/>
+      <c r="H45" s="93" t="n"/>
+      <c r="I45" s="93" t="n"/>
+      <c r="J45" s="93" t="n"/>
+      <c r="K45" s="93" t="n"/>
+      <c r="L45" s="89" t="n"/>
+    </row>
+    <row r="46" ht="16.95" customHeight="1" s="127">
+      <c r="A46" s="126" t="n">
         <v>21</v>
       </c>
-      <c r="B46" s="89" t="inlineStr">
+      <c r="B46" s="72" t="inlineStr">
         <is>
           <t>Personal con EPP completos y en buen estado</t>
         </is>
       </c>
-      <c r="C46" s="30" t="n"/>
-      <c r="D46" s="30" t="n"/>
-      <c r="E46" s="30" t="n"/>
-      <c r="F46" s="30" t="n"/>
-      <c r="G46" s="31" t="n"/>
-      <c r="H46" s="57" t="n"/>
-      <c r="I46" s="57" t="n"/>
-      <c r="J46" s="57" t="n"/>
-      <c r="K46" s="29" t="n"/>
-      <c r="L46" s="31" t="n"/>
-    </row>
-    <row r="47" ht="16.95" customHeight="1" s="70">
-      <c r="A47" s="57" t="n">
+      <c r="C46" s="93" t="n"/>
+      <c r="D46" s="93" t="n"/>
+      <c r="E46" s="93" t="n"/>
+      <c r="F46" s="93" t="n"/>
+      <c r="G46" s="89" t="n"/>
+      <c r="H46" s="126" t="n"/>
+      <c r="I46" s="126" t="n"/>
+      <c r="J46" s="126" t="n"/>
+      <c r="K46" s="76" t="n"/>
+      <c r="L46" s="89" t="n"/>
+    </row>
+    <row r="47" ht="16.95" customHeight="1" s="127">
+      <c r="A47" s="126" t="n">
         <v>22</v>
       </c>
-      <c r="B47" s="89" t="inlineStr">
+      <c r="B47" s="72" t="inlineStr">
         <is>
           <t>Personal afiliado a seguridad social y con capacitación vigente</t>
         </is>
       </c>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="30" t="n"/>
-      <c r="E47" s="30" t="n"/>
-      <c r="F47" s="30" t="n"/>
-      <c r="G47" s="31" t="n"/>
-      <c r="H47" s="57" t="n"/>
-      <c r="I47" s="57" t="n"/>
-      <c r="J47" s="57" t="n"/>
-      <c r="K47" s="29" t="n"/>
-      <c r="L47" s="31" t="n"/>
-    </row>
-    <row r="48" ht="16.95" customHeight="1" s="70">
-      <c r="A48" s="57" t="n">
+      <c r="C47" s="93" t="n"/>
+      <c r="D47" s="93" t="n"/>
+      <c r="E47" s="93" t="n"/>
+      <c r="F47" s="93" t="n"/>
+      <c r="G47" s="89" t="n"/>
+      <c r="H47" s="126" t="n"/>
+      <c r="I47" s="126" t="n"/>
+      <c r="J47" s="126" t="n"/>
+      <c r="K47" s="76" t="n"/>
+      <c r="L47" s="89" t="n"/>
+    </row>
+    <row r="48" ht="16.95" customHeight="1" s="127">
+      <c r="A48" s="126" t="n">
         <v>23</v>
       </c>
-      <c r="B48" s="89" t="inlineStr">
+      <c r="B48" s="72" t="inlineStr">
         <is>
           <t>Charla de seguridad realizada y registrada</t>
         </is>
       </c>
-      <c r="C48" s="30" t="n"/>
-      <c r="D48" s="30" t="n"/>
-      <c r="E48" s="30" t="n"/>
-      <c r="F48" s="30" t="n"/>
-      <c r="G48" s="31" t="n"/>
-      <c r="H48" s="57" t="n"/>
-      <c r="I48" s="57" t="n"/>
-      <c r="J48" s="57" t="n"/>
-      <c r="K48" s="29" t="n"/>
-      <c r="L48" s="31" t="n"/>
-    </row>
-    <row r="49" ht="21" customHeight="1" s="70">
-      <c r="A49" s="60" t="inlineStr">
+      <c r="C48" s="93" t="n"/>
+      <c r="D48" s="93" t="n"/>
+      <c r="E48" s="93" t="n"/>
+      <c r="F48" s="93" t="n"/>
+      <c r="G48" s="89" t="n"/>
+      <c r="H48" s="126" t="n"/>
+      <c r="I48" s="126" t="n"/>
+      <c r="J48" s="126" t="n"/>
+      <c r="K48" s="76" t="n"/>
+      <c r="L48" s="89" t="n"/>
+    </row>
+    <row r="49" ht="21" customHeight="1" s="127">
+      <c r="A49" s="310" t="inlineStr">
         <is>
           <t>TOTAL (cuántos aspectos se marcaron en cada columna)</t>
         </is>
       </c>
-      <c r="B49" s="30" t="n"/>
-      <c r="C49" s="30" t="n"/>
-      <c r="D49" s="30" t="n"/>
-      <c r="E49" s="30" t="n"/>
-      <c r="F49" s="30" t="n"/>
-      <c r="G49" s="31" t="n"/>
-      <c r="H49" s="58">
+      <c r="B49" s="104" t="n"/>
+      <c r="C49" s="104" t="n"/>
+      <c r="D49" s="104" t="n"/>
+      <c r="E49" s="104" t="n"/>
+      <c r="F49" s="104" t="n"/>
+      <c r="G49" s="94" t="n"/>
+      <c r="H49" s="313">
         <f>COUNTA(H19:H48)</f>
         <v/>
       </c>
-      <c r="I49" s="58">
+      <c r="I49" s="313">
         <f>COUNTA(I19:I48)</f>
         <v/>
       </c>
-      <c r="J49" s="58">
+      <c r="J49" s="313">
         <f>COUNTA(J19:J48)</f>
         <v/>
       </c>
-      <c r="K49" s="32">
+      <c r="K49" s="180">
         <f>IFERROR(H49/(H49+I49),"")</f>
         <v/>
       </c>
-      <c r="L49" s="31" t="n"/>
-    </row>
-    <row r="50" ht="16.05" customHeight="1" s="70">
-      <c r="A50" s="103" t="inlineStr">
+      <c r="L49" s="89" t="n"/>
+    </row>
+    <row r="50" ht="16.05" customHeight="1" s="127">
+      <c r="A50" s="255" t="inlineStr">
         <is>
           <t>% de cumplimiento = Cumple ÷ (Cumple + No cumple); los N/A no cuentan.</t>
         </is>
       </c>
-      <c r="B50" s="115" t="n"/>
-      <c r="C50" s="115" t="n"/>
-      <c r="D50" s="115" t="n"/>
-      <c r="E50" s="115" t="n"/>
-      <c r="F50" s="115" t="n"/>
-      <c r="G50" s="115" t="n"/>
-      <c r="H50" s="115" t="n"/>
-      <c r="I50" s="115" t="n"/>
-      <c r="J50" s="116" t="n"/>
-      <c r="K50" s="103" t="inlineStr">
+      <c r="B50" s="349" t="n"/>
+      <c r="C50" s="349" t="n"/>
+      <c r="D50" s="349" t="n"/>
+      <c r="E50" s="349" t="n"/>
+      <c r="F50" s="349" t="n"/>
+      <c r="G50" s="349" t="n"/>
+      <c r="H50" s="349" t="n"/>
+      <c r="I50" s="349" t="n"/>
+      <c r="J50" s="351" t="n"/>
+      <c r="K50" s="219" t="inlineStr">
         <is>
           <t>← % de cumplimiento</t>
         </is>
       </c>
-      <c r="L50" s="116" t="n"/>
-    </row>
-    <row r="51" ht="16.5" customHeight="1" s="70">
-      <c r="A51" s="54" t="inlineStr">
+      <c r="L50" s="357" t="n"/>
+    </row>
+    <row r="51" ht="16.5" customHeight="1" s="127">
+      <c r="A51" s="137" t="inlineStr">
         <is>
           <t>3. HALLAZGOS Y ACCIONES CORRECTIVAS</t>
         </is>
       </c>
-      <c r="B51" s="38" t="n"/>
-      <c r="C51" s="38" t="n"/>
-      <c r="D51" s="38" t="n"/>
-      <c r="E51" s="38" t="n"/>
-      <c r="F51" s="38" t="n"/>
-      <c r="G51" s="38" t="n"/>
-      <c r="H51" s="38" t="n"/>
-      <c r="I51" s="38" t="n"/>
-      <c r="J51" s="38" t="n"/>
-      <c r="K51" s="38" t="n"/>
-      <c r="L51" s="47" t="n"/>
-    </row>
-    <row r="52" ht="28.05" customHeight="1" s="70">
-      <c r="A52" s="34" t="inlineStr">
+      <c r="B51" s="98" t="n"/>
+      <c r="C51" s="98" t="n"/>
+      <c r="D51" s="98" t="n"/>
+      <c r="E51" s="98" t="n"/>
+      <c r="F51" s="98" t="n"/>
+      <c r="G51" s="98" t="n"/>
+      <c r="H51" s="98" t="n"/>
+      <c r="I51" s="98" t="n"/>
+      <c r="J51" s="98" t="n"/>
+      <c r="K51" s="98" t="n"/>
+      <c r="L51" s="97" t="n"/>
+    </row>
+    <row r="52" ht="28.05" customHeight="1" s="127">
+      <c r="A52" s="74" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B52" s="34" t="inlineStr">
+      <c r="B52" s="74" t="inlineStr">
         <is>
           <t>Hallazgo</t>
         </is>
       </c>
-      <c r="C52" s="30" t="n"/>
-      <c r="D52" s="31" t="n"/>
-      <c r="E52" s="34" t="inlineStr">
+      <c r="C52" s="93" t="n"/>
+      <c r="D52" s="89" t="n"/>
+      <c r="E52" s="74" t="inlineStr">
         <is>
           <t>Nivel de riesgo</t>
         </is>
       </c>
-      <c r="F52" s="34" t="inlineStr">
+      <c r="F52" s="74" t="inlineStr">
         <is>
           <t>Acción correctiva</t>
         </is>
       </c>
-      <c r="G52" s="30" t="n"/>
-      <c r="H52" s="31" t="n"/>
-      <c r="I52" s="34" t="inlineStr">
+      <c r="G52" s="93" t="n"/>
+      <c r="H52" s="89" t="n"/>
+      <c r="I52" s="74" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="J52" s="31" t="n"/>
-      <c r="K52" s="34" t="inlineStr">
+      <c r="J52" s="89" t="n"/>
+      <c r="K52" s="74" t="inlineStr">
         <is>
           <t>Fecha límite</t>
         </is>
       </c>
-      <c r="L52" s="34" t="inlineStr">
+      <c r="L52" s="74" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="34.05" customHeight="1" s="70">
-      <c r="A53" s="57" t="n">
+    <row r="53" ht="34.05" customHeight="1" s="127">
+      <c r="A53" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B53" s="89" t="n"/>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="57" t="n"/>
-      <c r="F53" s="89" t="n"/>
-      <c r="G53" s="30" t="n"/>
-      <c r="H53" s="31" t="n"/>
-      <c r="I53" s="29" t="n"/>
-      <c r="J53" s="31" t="n"/>
-      <c r="K53" s="27" t="n"/>
-      <c r="L53" s="57" t="n"/>
-    </row>
-    <row r="54" ht="34.05" customHeight="1" s="70">
-      <c r="A54" s="57" t="n">
+      <c r="B53" s="72" t="n"/>
+      <c r="C53" s="93" t="n"/>
+      <c r="D53" s="89" t="n"/>
+      <c r="E53" s="126" t="n"/>
+      <c r="F53" s="72" t="n"/>
+      <c r="G53" s="93" t="n"/>
+      <c r="H53" s="89" t="n"/>
+      <c r="I53" s="76" t="n"/>
+      <c r="J53" s="89" t="n"/>
+      <c r="K53" s="23" t="n"/>
+      <c r="L53" s="126" t="n"/>
+    </row>
+    <row r="54" ht="34.05" customHeight="1" s="127">
+      <c r="A54" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B54" s="89" t="n"/>
-      <c r="C54" s="30" t="n"/>
-      <c r="D54" s="31" t="n"/>
-      <c r="E54" s="57" t="n"/>
-      <c r="F54" s="89" t="n"/>
-      <c r="G54" s="30" t="n"/>
-      <c r="H54" s="31" t="n"/>
-      <c r="I54" s="29" t="n"/>
-      <c r="J54" s="31" t="n"/>
-      <c r="K54" s="27" t="n"/>
-      <c r="L54" s="57" t="n"/>
-    </row>
-    <row r="55" ht="34.05" customHeight="1" s="70">
-      <c r="A55" s="57" t="n">
+      <c r="B54" s="72" t="n"/>
+      <c r="C54" s="93" t="n"/>
+      <c r="D54" s="89" t="n"/>
+      <c r="E54" s="126" t="n"/>
+      <c r="F54" s="72" t="n"/>
+      <c r="G54" s="93" t="n"/>
+      <c r="H54" s="89" t="n"/>
+      <c r="I54" s="76" t="n"/>
+      <c r="J54" s="89" t="n"/>
+      <c r="K54" s="23" t="n"/>
+      <c r="L54" s="126" t="n"/>
+    </row>
+    <row r="55" ht="34.05" customHeight="1" s="127">
+      <c r="A55" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B55" s="89" t="n"/>
-      <c r="C55" s="30" t="n"/>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="57" t="n"/>
-      <c r="F55" s="89" t="n"/>
-      <c r="G55" s="30" t="n"/>
-      <c r="H55" s="31" t="n"/>
-      <c r="I55" s="29" t="n"/>
-      <c r="J55" s="31" t="n"/>
-      <c r="K55" s="27" t="n"/>
-      <c r="L55" s="57" t="n"/>
-    </row>
-    <row r="56" ht="34.05" customHeight="1" s="70">
-      <c r="A56" s="57" t="n">
+      <c r="B55" s="72" t="n"/>
+      <c r="C55" s="93" t="n"/>
+      <c r="D55" s="89" t="n"/>
+      <c r="E55" s="126" t="n"/>
+      <c r="F55" s="72" t="n"/>
+      <c r="G55" s="93" t="n"/>
+      <c r="H55" s="89" t="n"/>
+      <c r="I55" s="76" t="n"/>
+      <c r="J55" s="89" t="n"/>
+      <c r="K55" s="23" t="n"/>
+      <c r="L55" s="126" t="n"/>
+    </row>
+    <row r="56" ht="34.05" customHeight="1" s="127">
+      <c r="A56" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B56" s="89" t="n"/>
-      <c r="C56" s="30" t="n"/>
-      <c r="D56" s="31" t="n"/>
-      <c r="E56" s="57" t="n"/>
-      <c r="F56" s="89" t="n"/>
-      <c r="G56" s="30" t="n"/>
-      <c r="H56" s="31" t="n"/>
-      <c r="I56" s="29" t="n"/>
-      <c r="J56" s="31" t="n"/>
-      <c r="K56" s="27" t="n"/>
-      <c r="L56" s="57" t="n"/>
-    </row>
-    <row r="57" ht="34.05" customHeight="1" s="70">
-      <c r="A57" s="57" t="n">
+      <c r="B56" s="72" t="n"/>
+      <c r="C56" s="93" t="n"/>
+      <c r="D56" s="89" t="n"/>
+      <c r="E56" s="126" t="n"/>
+      <c r="F56" s="72" t="n"/>
+      <c r="G56" s="93" t="n"/>
+      <c r="H56" s="89" t="n"/>
+      <c r="I56" s="76" t="n"/>
+      <c r="J56" s="89" t="n"/>
+      <c r="K56" s="23" t="n"/>
+      <c r="L56" s="126" t="n"/>
+    </row>
+    <row r="57" ht="34.05" customHeight="1" s="127">
+      <c r="A57" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B57" s="89" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="57" t="n"/>
-      <c r="F57" s="89" t="n"/>
-      <c r="G57" s="30" t="n"/>
-      <c r="H57" s="31" t="n"/>
-      <c r="I57" s="29" t="n"/>
-      <c r="J57" s="31" t="n"/>
-      <c r="K57" s="27" t="n"/>
-      <c r="L57" s="57" t="n"/>
-    </row>
-    <row r="58" ht="34.05" customHeight="1" s="70">
-      <c r="A58" s="57" t="n">
+      <c r="B57" s="72" t="n"/>
+      <c r="C57" s="93" t="n"/>
+      <c r="D57" s="89" t="n"/>
+      <c r="E57" s="126" t="n"/>
+      <c r="F57" s="72" t="n"/>
+      <c r="G57" s="93" t="n"/>
+      <c r="H57" s="89" t="n"/>
+      <c r="I57" s="76" t="n"/>
+      <c r="J57" s="89" t="n"/>
+      <c r="K57" s="23" t="n"/>
+      <c r="L57" s="126" t="n"/>
+    </row>
+    <row r="58" ht="34.05" customHeight="1" s="127">
+      <c r="A58" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B58" s="89" t="n"/>
-      <c r="C58" s="30" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="57" t="n"/>
-      <c r="F58" s="89" t="n"/>
-      <c r="G58" s="30" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="29" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="27" t="n"/>
-      <c r="L58" s="57" t="n"/>
-    </row>
-    <row r="59" ht="34.05" customHeight="1" s="70">
-      <c r="A59" s="57" t="n">
+      <c r="B58" s="72" t="n"/>
+      <c r="C58" s="93" t="n"/>
+      <c r="D58" s="89" t="n"/>
+      <c r="E58" s="126" t="n"/>
+      <c r="F58" s="72" t="n"/>
+      <c r="G58" s="93" t="n"/>
+      <c r="H58" s="89" t="n"/>
+      <c r="I58" s="76" t="n"/>
+      <c r="J58" s="89" t="n"/>
+      <c r="K58" s="23" t="n"/>
+      <c r="L58" s="126" t="n"/>
+    </row>
+    <row r="59" ht="34.05" customHeight="1" s="127">
+      <c r="A59" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B59" s="89" t="n"/>
-      <c r="C59" s="30" t="n"/>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="57" t="n"/>
-      <c r="F59" s="89" t="n"/>
-      <c r="G59" s="30" t="n"/>
-      <c r="H59" s="31" t="n"/>
-      <c r="I59" s="29" t="n"/>
-      <c r="J59" s="31" t="n"/>
-      <c r="K59" s="27" t="n"/>
-      <c r="L59" s="57" t="n"/>
-    </row>
-    <row r="60" ht="34.05" customHeight="1" s="70">
-      <c r="A60" s="57" t="n">
+      <c r="B59" s="72" t="n"/>
+      <c r="C59" s="93" t="n"/>
+      <c r="D59" s="89" t="n"/>
+      <c r="E59" s="126" t="n"/>
+      <c r="F59" s="72" t="n"/>
+      <c r="G59" s="93" t="n"/>
+      <c r="H59" s="89" t="n"/>
+      <c r="I59" s="76" t="n"/>
+      <c r="J59" s="89" t="n"/>
+      <c r="K59" s="23" t="n"/>
+      <c r="L59" s="126" t="n"/>
+    </row>
+    <row r="60" ht="34.05" customHeight="1" s="127">
+      <c r="A60" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B60" s="89" t="n"/>
-      <c r="C60" s="30" t="n"/>
-      <c r="D60" s="31" t="n"/>
-      <c r="E60" s="57" t="n"/>
-      <c r="F60" s="89" t="n"/>
-      <c r="G60" s="30" t="n"/>
-      <c r="H60" s="31" t="n"/>
-      <c r="I60" s="29" t="n"/>
-      <c r="J60" s="31" t="n"/>
-      <c r="K60" s="27" t="n"/>
-      <c r="L60" s="57" t="n"/>
-    </row>
-    <row r="61" ht="34.05" customHeight="1" s="70">
-      <c r="A61" s="57" t="n">
+      <c r="B60" s="72" t="n"/>
+      <c r="C60" s="93" t="n"/>
+      <c r="D60" s="89" t="n"/>
+      <c r="E60" s="126" t="n"/>
+      <c r="F60" s="72" t="n"/>
+      <c r="G60" s="93" t="n"/>
+      <c r="H60" s="89" t="n"/>
+      <c r="I60" s="76" t="n"/>
+      <c r="J60" s="89" t="n"/>
+      <c r="K60" s="23" t="n"/>
+      <c r="L60" s="126" t="n"/>
+    </row>
+    <row r="61" ht="34.05" customHeight="1" s="127">
+      <c r="A61" s="126" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="89" t="n"/>
-      <c r="C61" s="30" t="n"/>
-      <c r="D61" s="31" t="n"/>
-      <c r="E61" s="57" t="n"/>
-      <c r="F61" s="89" t="n"/>
-      <c r="G61" s="30" t="n"/>
-      <c r="H61" s="31" t="n"/>
-      <c r="I61" s="29" t="n"/>
-      <c r="J61" s="31" t="n"/>
-      <c r="K61" s="27" t="n"/>
-      <c r="L61" s="57" t="n"/>
-    </row>
-    <row r="62" ht="34.05" customHeight="1" s="70">
-      <c r="A62" s="57" t="n">
+      <c r="B61" s="72" t="n"/>
+      <c r="C61" s="93" t="n"/>
+      <c r="D61" s="89" t="n"/>
+      <c r="E61" s="126" t="n"/>
+      <c r="F61" s="72" t="n"/>
+      <c r="G61" s="93" t="n"/>
+      <c r="H61" s="89" t="n"/>
+      <c r="I61" s="76" t="n"/>
+      <c r="J61" s="89" t="n"/>
+      <c r="K61" s="23" t="n"/>
+      <c r="L61" s="126" t="n"/>
+    </row>
+    <row r="62" ht="34.05" customHeight="1" s="127">
+      <c r="A62" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="B62" s="89" t="n"/>
-      <c r="C62" s="30" t="n"/>
-      <c r="D62" s="31" t="n"/>
-      <c r="E62" s="57" t="n"/>
-      <c r="F62" s="89" t="n"/>
-      <c r="G62" s="30" t="n"/>
-      <c r="H62" s="31" t="n"/>
-      <c r="I62" s="29" t="n"/>
-      <c r="J62" s="31" t="n"/>
-      <c r="K62" s="27" t="n"/>
-      <c r="L62" s="57" t="n"/>
-    </row>
-    <row r="63" ht="16.5" customHeight="1" s="70">
-      <c r="A63" s="54" t="inlineStr">
+      <c r="B62" s="72" t="n"/>
+      <c r="C62" s="93" t="n"/>
+      <c r="D62" s="89" t="n"/>
+      <c r="E62" s="126" t="n"/>
+      <c r="F62" s="72" t="n"/>
+      <c r="G62" s="93" t="n"/>
+      <c r="H62" s="89" t="n"/>
+      <c r="I62" s="76" t="n"/>
+      <c r="J62" s="89" t="n"/>
+      <c r="K62" s="23" t="n"/>
+      <c r="L62" s="126" t="n"/>
+    </row>
+    <row r="63" ht="16.5" customHeight="1" s="127">
+      <c r="A63" s="137" t="inlineStr">
         <is>
           <t>4. OBSERVACIONES GENERALES</t>
         </is>
       </c>
-      <c r="B63" s="38" t="n"/>
-      <c r="C63" s="38" t="n"/>
-      <c r="D63" s="38" t="n"/>
-      <c r="E63" s="38" t="n"/>
-      <c r="F63" s="38" t="n"/>
-      <c r="G63" s="38" t="n"/>
-      <c r="H63" s="38" t="n"/>
-      <c r="I63" s="38" t="n"/>
-      <c r="J63" s="38" t="n"/>
-      <c r="K63" s="38" t="n"/>
-      <c r="L63" s="47" t="n"/>
-    </row>
-    <row r="64" ht="30" customHeight="1" s="70">
-      <c r="A64" s="52" t="n"/>
-      <c r="B64" s="56" t="n"/>
-      <c r="C64" s="56" t="n"/>
-      <c r="D64" s="56" t="n"/>
-      <c r="E64" s="56" t="n"/>
-      <c r="F64" s="56" t="n"/>
-      <c r="G64" s="56" t="n"/>
-      <c r="H64" s="56" t="n"/>
-      <c r="I64" s="56" t="n"/>
-      <c r="J64" s="56" t="n"/>
-      <c r="K64" s="56" t="n"/>
-      <c r="L64" s="45" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1" s="70">
-      <c r="A65" s="37" t="n"/>
-      <c r="B65" s="38" t="n"/>
-      <c r="C65" s="38" t="n"/>
-      <c r="D65" s="38" t="n"/>
-      <c r="E65" s="38" t="n"/>
-      <c r="F65" s="38" t="n"/>
-      <c r="G65" s="38" t="n"/>
-      <c r="H65" s="38" t="n"/>
-      <c r="I65" s="38" t="n"/>
-      <c r="J65" s="38" t="n"/>
-      <c r="K65" s="38" t="n"/>
-      <c r="L65" s="47" t="n"/>
-    </row>
-    <row r="66" ht="16.5" customHeight="1" s="70">
-      <c r="A66" s="54" t="inlineStr">
+      <c r="B63" s="98" t="n"/>
+      <c r="C63" s="98" t="n"/>
+      <c r="D63" s="98" t="n"/>
+      <c r="E63" s="98" t="n"/>
+      <c r="F63" s="98" t="n"/>
+      <c r="G63" s="98" t="n"/>
+      <c r="H63" s="98" t="n"/>
+      <c r="I63" s="98" t="n"/>
+      <c r="J63" s="98" t="n"/>
+      <c r="K63" s="98" t="n"/>
+      <c r="L63" s="97" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1" s="127">
+      <c r="A64" s="100" t="n"/>
+      <c r="B64" s="104" t="n"/>
+      <c r="C64" s="104" t="n"/>
+      <c r="D64" s="104" t="n"/>
+      <c r="E64" s="104" t="n"/>
+      <c r="F64" s="104" t="n"/>
+      <c r="G64" s="104" t="n"/>
+      <c r="H64" s="104" t="n"/>
+      <c r="I64" s="104" t="n"/>
+      <c r="J64" s="104" t="n"/>
+      <c r="K64" s="104" t="n"/>
+      <c r="L64" s="94" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1" s="127">
+      <c r="A65" s="96" t="n"/>
+      <c r="B65" s="98" t="n"/>
+      <c r="C65" s="98" t="n"/>
+      <c r="D65" s="98" t="n"/>
+      <c r="E65" s="98" t="n"/>
+      <c r="F65" s="98" t="n"/>
+      <c r="G65" s="98" t="n"/>
+      <c r="H65" s="98" t="n"/>
+      <c r="I65" s="98" t="n"/>
+      <c r="J65" s="98" t="n"/>
+      <c r="K65" s="98" t="n"/>
+      <c r="L65" s="97" t="n"/>
+    </row>
+    <row r="66" ht="16.5" customHeight="1" s="127">
+      <c r="A66" s="227" t="inlineStr">
         <is>
           <t>5. FIRMAS</t>
         </is>
       </c>
-      <c r="B66" s="38" t="n"/>
-      <c r="C66" s="38" t="n"/>
-      <c r="D66" s="38" t="n"/>
-      <c r="E66" s="38" t="n"/>
-      <c r="F66" s="38" t="n"/>
-      <c r="G66" s="38" t="n"/>
-      <c r="H66" s="38" t="n"/>
-      <c r="I66" s="38" t="n"/>
-      <c r="J66" s="38" t="n"/>
-      <c r="K66" s="38" t="n"/>
-      <c r="L66" s="47" t="n"/>
-    </row>
-    <row r="67" ht="18" customHeight="1" s="70">
-      <c r="A67" s="51" t="inlineStr">
+      <c r="L66" s="92" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1" s="127">
+      <c r="A67" s="263" t="inlineStr">
         <is>
           <t>INSPECTOR</t>
         </is>
       </c>
-      <c r="B67" s="30" t="n"/>
-      <c r="C67" s="30" t="n"/>
-      <c r="D67" s="30" t="n"/>
-      <c r="E67" s="30" t="n"/>
-      <c r="F67" s="31" t="n"/>
-      <c r="G67" s="51" t="inlineStr">
+      <c r="B67" s="347" t="n"/>
+      <c r="C67" s="347" t="n"/>
+      <c r="D67" s="347" t="n"/>
+      <c r="E67" s="347" t="n"/>
+      <c r="F67" s="348" t="n"/>
+      <c r="G67" s="263" t="inlineStr">
         <is>
           <t>RESPONSABLE DEL ÁREA / RESIDENTE DE OBRA</t>
         </is>
       </c>
-      <c r="H67" s="30" t="n"/>
-      <c r="I67" s="30" t="n"/>
-      <c r="J67" s="30" t="n"/>
-      <c r="K67" s="30" t="n"/>
-      <c r="L67" s="31" t="n"/>
-    </row>
-    <row r="68" ht="42" customHeight="1" s="70">
-      <c r="A68" s="39" t="inlineStr">
+      <c r="H67" s="347" t="n"/>
+      <c r="I67" s="347" t="n"/>
+      <c r="J67" s="347" t="n"/>
+      <c r="K67" s="347" t="n"/>
+      <c r="L67" s="348" t="n"/>
+    </row>
+    <row r="68" ht="42" customHeight="1" s="127">
+      <c r="A68" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B68" s="31" t="n"/>
-      <c r="C68" s="43" t="n"/>
-      <c r="D68" s="30" t="n"/>
-      <c r="E68" s="30" t="n"/>
-      <c r="F68" s="31" t="n"/>
-      <c r="G68" s="39" t="inlineStr">
+      <c r="B68" s="97" t="n"/>
+      <c r="C68" s="301" t="n"/>
+      <c r="D68" s="98" t="n"/>
+      <c r="E68" s="98" t="n"/>
+      <c r="F68" s="97" t="n"/>
+      <c r="G68" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="H68" s="31" t="n"/>
-      <c r="I68" s="43" t="n"/>
-      <c r="J68" s="30" t="n"/>
-      <c r="K68" s="30" t="n"/>
-      <c r="L68" s="31" t="n"/>
-    </row>
-    <row r="69" ht="21" customHeight="1" s="70">
-      <c r="A69" s="39" t="inlineStr">
+      <c r="H68" s="97" t="n"/>
+      <c r="I68" s="301" t="n"/>
+      <c r="J68" s="98" t="n"/>
+      <c r="K68" s="98" t="n"/>
+      <c r="L68" s="97" t="n"/>
+    </row>
+    <row r="69" ht="21" customHeight="1" s="127">
+      <c r="A69" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B69" s="31" t="n"/>
-      <c r="C69" s="43" t="n"/>
-      <c r="D69" s="30" t="n"/>
-      <c r="E69" s="30" t="n"/>
-      <c r="F69" s="31" t="n"/>
-      <c r="G69" s="39" t="inlineStr">
+      <c r="B69" s="89" t="n"/>
+      <c r="C69" s="68" t="n"/>
+      <c r="D69" s="93" t="n"/>
+      <c r="E69" s="93" t="n"/>
+      <c r="F69" s="89" t="n"/>
+      <c r="G69" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="H69" s="31" t="n"/>
-      <c r="I69" s="43" t="n"/>
-      <c r="J69" s="30" t="n"/>
-      <c r="K69" s="30" t="n"/>
-      <c r="L69" s="31" t="n"/>
-    </row>
-    <row r="70" ht="21" customHeight="1" s="70">
-      <c r="A70" s="39" t="inlineStr">
+      <c r="H69" s="89" t="n"/>
+      <c r="I69" s="68" t="n"/>
+      <c r="J69" s="93" t="n"/>
+      <c r="K69" s="93" t="n"/>
+      <c r="L69" s="89" t="n"/>
+    </row>
+    <row r="70" ht="21" customHeight="1" s="127">
+      <c r="A70" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B70" s="31" t="n"/>
-      <c r="C70" s="43" t="n"/>
-      <c r="D70" s="30" t="n"/>
-      <c r="E70" s="30" t="n"/>
-      <c r="F70" s="31" t="n"/>
-      <c r="G70" s="39" t="inlineStr">
+      <c r="B70" s="89" t="n"/>
+      <c r="C70" s="68" t="n"/>
+      <c r="D70" s="93" t="n"/>
+      <c r="E70" s="93" t="n"/>
+      <c r="F70" s="89" t="n"/>
+      <c r="G70" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="H70" s="31" t="n"/>
-      <c r="I70" s="43" t="n"/>
-      <c r="J70" s="30" t="n"/>
-      <c r="K70" s="30" t="n"/>
-      <c r="L70" s="31" t="n"/>
+      <c r="H70" s="89" t="n"/>
+      <c r="I70" s="68" t="n"/>
+      <c r="J70" s="93" t="n"/>
+      <c r="K70" s="93" t="n"/>
+      <c r="L70" s="89" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="61" t="inlineStr">
+      <c r="A71" s="25" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
         </is>
       </c>
-      <c r="G71" s="63">
+      <c r="G71" s="105">
         <f>K5</f>
         <v/>
       </c>

--- a/public/plantilla-inspecciones.xlsx
+++ b/public/plantilla-inspecciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inspecciones" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="39">
+  <numFmts count="0"/>
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -297,6 +298,10 @@
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -1024,7 +1029,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="377">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1928,6 +1933,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2438,8 +2501,12 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="15.77734375" customWidth="1" style="127" min="1" max="2"/>
+    <col width="13" customWidth="1" style="127" min="2" max="2"/>
     <col width="13" customWidth="1" style="127" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="127" min="4" max="10"/>
+    <col width="13" customWidth="1" style="127" min="5" max="5"/>
+    <col width="13" customWidth="1" style="127" min="6" max="6"/>
+    <col width="13" customWidth="1" style="127" min="7" max="7"/>
     <col width="12" customWidth="1" style="127" min="11" max="11"/>
     <col width="13" customWidth="1" style="127" min="12" max="12"/>
     <col width="8.88671875" customWidth="1" style="127" min="13" max="16384"/>
@@ -2600,16 +2667,16 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="161" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="93" t="n"/>
-      <c r="J11" s="93" t="n"/>
-      <c r="K11" s="93" t="n"/>
-      <c r="L11" s="89" t="n"/>
+      <c r="C11" s="360" t="n"/>
+      <c r="D11" s="361" t="n"/>
+      <c r="E11" s="361" t="n"/>
+      <c r="F11" s="361" t="n"/>
+      <c r="G11" s="361" t="n"/>
+      <c r="H11" s="361" t="n"/>
+      <c r="I11" s="361" t="n"/>
+      <c r="J11" s="361" t="n"/>
+      <c r="K11" s="361" t="n"/>
+      <c r="L11" s="362" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2618,20 +2685,20 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="363" t="n"/>
+      <c r="D12" s="361" t="n"/>
+      <c r="E12" s="361" t="n"/>
+      <c r="F12" s="361" t="n"/>
+      <c r="G12" s="362" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="89" t="n"/>
-      <c r="J12" s="68" t="n"/>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="89" t="n"/>
+      <c r="J12" s="363" t="n"/>
+      <c r="K12" s="361" t="n"/>
+      <c r="L12" s="362" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2640,25 +2707,25 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="69" t="n"/>
+      <c r="C13" s="364" t="n"/>
       <c r="D13" s="59" t="inlineStr">
         <is>
           <t>Hora inicio</t>
         </is>
       </c>
-      <c r="E13" s="69" t="n"/>
+      <c r="E13" s="364" t="n"/>
       <c r="F13" s="59" t="inlineStr">
         <is>
           <t>Hora fin</t>
         </is>
       </c>
-      <c r="G13" s="69" t="n"/>
+      <c r="G13" s="364" t="n"/>
       <c r="H13" s="59" t="inlineStr">
         <is>
           <t>Duración</t>
         </is>
       </c>
-      <c r="I13" s="69">
+      <c r="I13" s="365">
         <f>IFERROR(IF(OR(E13="",G13=""),"",TEXT(G13-E13,"h:mm")),"")</f>
         <v/>
       </c>
@@ -2667,8 +2734,8 @@
           <t>N° de inspección</t>
         </is>
       </c>
-      <c r="K13" s="69" t="n"/>
-      <c r="L13" s="89" t="n"/>
+      <c r="K13" s="364" t="n"/>
+      <c r="L13" s="362" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="127">
       <c r="A14" s="59" t="inlineStr">
@@ -2677,20 +2744,20 @@
         </is>
       </c>
       <c r="B14" s="89" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="93" t="n"/>
-      <c r="E14" s="93" t="n"/>
-      <c r="F14" s="93" t="n"/>
-      <c r="G14" s="89" t="n"/>
+      <c r="C14" s="363" t="n"/>
+      <c r="D14" s="361" t="n"/>
+      <c r="E14" s="361" t="n"/>
+      <c r="F14" s="361" t="n"/>
+      <c r="G14" s="362" t="n"/>
       <c r="H14" s="59" t="inlineStr">
         <is>
           <t>Área / frente inspeccionado</t>
         </is>
       </c>
       <c r="I14" s="89" t="n"/>
-      <c r="J14" s="68" t="n"/>
-      <c r="K14" s="93" t="n"/>
-      <c r="L14" s="89" t="n"/>
+      <c r="J14" s="363" t="n"/>
+      <c r="K14" s="361" t="n"/>
+      <c r="L14" s="362" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="127">
       <c r="A15" s="59" t="inlineStr">
@@ -2699,20 +2766,20 @@
         </is>
       </c>
       <c r="B15" s="89" t="n"/>
-      <c r="C15" s="68" t="n"/>
-      <c r="D15" s="93" t="n"/>
-      <c r="E15" s="93" t="n"/>
-      <c r="F15" s="93" t="n"/>
-      <c r="G15" s="89" t="n"/>
+      <c r="C15" s="363" t="n"/>
+      <c r="D15" s="361" t="n"/>
+      <c r="E15" s="361" t="n"/>
+      <c r="F15" s="361" t="n"/>
+      <c r="G15" s="362" t="n"/>
       <c r="H15" s="59" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
       <c r="I15" s="89" t="n"/>
-      <c r="J15" s="68" t="n"/>
-      <c r="K15" s="93" t="n"/>
-      <c r="L15" s="89" t="n"/>
+      <c r="J15" s="363" t="n"/>
+      <c r="K15" s="361" t="n"/>
+      <c r="L15" s="362" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="127">
       <c r="A16" s="59" t="inlineStr">
@@ -2721,20 +2788,20 @@
         </is>
       </c>
       <c r="B16" s="89" t="n"/>
-      <c r="C16" s="68" t="n"/>
-      <c r="D16" s="93" t="n"/>
-      <c r="E16" s="93" t="n"/>
-      <c r="F16" s="93" t="n"/>
-      <c r="G16" s="89" t="n"/>
+      <c r="C16" s="363" t="n"/>
+      <c r="D16" s="361" t="n"/>
+      <c r="E16" s="361" t="n"/>
+      <c r="F16" s="361" t="n"/>
+      <c r="G16" s="362" t="n"/>
       <c r="H16" s="59" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
       <c r="I16" s="89" t="n"/>
-      <c r="J16" s="68" t="n"/>
-      <c r="K16" s="93" t="n"/>
-      <c r="L16" s="89" t="n"/>
+      <c r="J16" s="363" t="n"/>
+      <c r="K16" s="361" t="n"/>
+      <c r="L16" s="362" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="127">
       <c r="A17" s="227" t="inlineStr">
@@ -2801,10 +2868,10 @@
       <c r="L19" s="97" t="n"/>
     </row>
     <row r="20" ht="16.95" customHeight="1" s="127">
-      <c r="A20" s="126" t="n">
+      <c r="A20" s="366" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="72" t="inlineStr">
+      <c r="B20" s="367" t="inlineStr">
         <is>
           <t>Áreas de trabajo y de circulación despejadas</t>
         </is>
@@ -2814,17 +2881,17 @@
       <c r="E20" s="93" t="n"/>
       <c r="F20" s="93" t="n"/>
       <c r="G20" s="89" t="n"/>
-      <c r="H20" s="126" t="n"/>
-      <c r="I20" s="126" t="n"/>
-      <c r="J20" s="126" t="n"/>
-      <c r="K20" s="76" t="n"/>
-      <c r="L20" s="89" t="n"/>
+      <c r="H20" s="368" t="n"/>
+      <c r="I20" s="368" t="n"/>
+      <c r="J20" s="368" t="n"/>
+      <c r="K20" s="363" t="n"/>
+      <c r="L20" s="362" t="n"/>
     </row>
     <row r="21" ht="16.95" customHeight="1" s="127">
-      <c r="A21" s="126" t="n">
+      <c r="A21" s="366" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="72" t="inlineStr">
+      <c r="B21" s="367" t="inlineStr">
         <is>
           <t>Materiales apilados y almacenados de forma segura</t>
         </is>
@@ -2834,17 +2901,17 @@
       <c r="E21" s="93" t="n"/>
       <c r="F21" s="93" t="n"/>
       <c r="G21" s="89" t="n"/>
-      <c r="H21" s="126" t="n"/>
-      <c r="I21" s="126" t="n"/>
-      <c r="J21" s="126" t="n"/>
-      <c r="K21" s="76" t="n"/>
-      <c r="L21" s="89" t="n"/>
+      <c r="H21" s="368" t="n"/>
+      <c r="I21" s="368" t="n"/>
+      <c r="J21" s="368" t="n"/>
+      <c r="K21" s="363" t="n"/>
+      <c r="L21" s="362" t="n"/>
     </row>
     <row r="22" ht="16.95" customHeight="1" s="127">
-      <c r="A22" s="126" t="n">
+      <c r="A22" s="366" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="72" t="inlineStr">
+      <c r="B22" s="367" t="inlineStr">
         <is>
           <t>Residuos clasificados y recipientes disponibles</t>
         </is>
@@ -2854,17 +2921,17 @@
       <c r="E22" s="93" t="n"/>
       <c r="F22" s="93" t="n"/>
       <c r="G22" s="89" t="n"/>
-      <c r="H22" s="126" t="n"/>
-      <c r="I22" s="126" t="n"/>
-      <c r="J22" s="126" t="n"/>
-      <c r="K22" s="76" t="n"/>
-      <c r="L22" s="89" t="n"/>
+      <c r="H22" s="368" t="n"/>
+      <c r="I22" s="368" t="n"/>
+      <c r="J22" s="368" t="n"/>
+      <c r="K22" s="363" t="n"/>
+      <c r="L22" s="362" t="n"/>
     </row>
     <row r="23" ht="16.95" customHeight="1" s="127">
-      <c r="A23" s="126" t="n">
+      <c r="A23" s="366" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="72" t="inlineStr">
+      <c r="B23" s="367" t="inlineStr">
         <is>
           <t>Baños, comedor y campamento en condiciones de higiene</t>
         </is>
@@ -2874,11 +2941,11 @@
       <c r="E23" s="93" t="n"/>
       <c r="F23" s="93" t="n"/>
       <c r="G23" s="89" t="n"/>
-      <c r="H23" s="126" t="n"/>
-      <c r="I23" s="126" t="n"/>
-      <c r="J23" s="126" t="n"/>
-      <c r="K23" s="76" t="n"/>
-      <c r="L23" s="89" t="n"/>
+      <c r="H23" s="368" t="n"/>
+      <c r="I23" s="368" t="n"/>
+      <c r="J23" s="368" t="n"/>
+      <c r="K23" s="363" t="n"/>
+      <c r="L23" s="362" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="127">
       <c r="A24" s="162" t="inlineStr">
@@ -2899,10 +2966,10 @@
       <c r="L24" s="89" t="n"/>
     </row>
     <row r="25" ht="16.95" customHeight="1" s="127">
-      <c r="A25" s="126" t="n">
+      <c r="A25" s="366" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="72" t="inlineStr">
+      <c r="B25" s="367" t="inlineStr">
         <is>
           <t>Señalización de seguridad visible y completa</t>
         </is>
@@ -2912,17 +2979,17 @@
       <c r="E25" s="93" t="n"/>
       <c r="F25" s="93" t="n"/>
       <c r="G25" s="89" t="n"/>
-      <c r="H25" s="126" t="n"/>
-      <c r="I25" s="126" t="n"/>
-      <c r="J25" s="126" t="n"/>
-      <c r="K25" s="76" t="n"/>
-      <c r="L25" s="89" t="n"/>
+      <c r="H25" s="368" t="n"/>
+      <c r="I25" s="368" t="n"/>
+      <c r="J25" s="368" t="n"/>
+      <c r="K25" s="363" t="n"/>
+      <c r="L25" s="362" t="n"/>
     </row>
     <row r="26" ht="16.95" customHeight="1" s="127">
-      <c r="A26" s="126" t="n">
+      <c r="A26" s="366" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="72" t="inlineStr">
+      <c r="B26" s="367" t="inlineStr">
         <is>
           <t>Áreas de riesgo demarcadas y cerradas</t>
         </is>
@@ -2932,17 +2999,17 @@
       <c r="E26" s="93" t="n"/>
       <c r="F26" s="93" t="n"/>
       <c r="G26" s="89" t="n"/>
-      <c r="H26" s="126" t="n"/>
-      <c r="I26" s="126" t="n"/>
-      <c r="J26" s="126" t="n"/>
-      <c r="K26" s="76" t="n"/>
-      <c r="L26" s="89" t="n"/>
+      <c r="H26" s="368" t="n"/>
+      <c r="I26" s="368" t="n"/>
+      <c r="J26" s="368" t="n"/>
+      <c r="K26" s="363" t="n"/>
+      <c r="L26" s="362" t="n"/>
     </row>
     <row r="27" ht="16.95" customHeight="1" s="127">
-      <c r="A27" s="126" t="n">
+      <c r="A27" s="366" t="n">
         <v>7</v>
       </c>
-      <c r="B27" s="72" t="inlineStr">
+      <c r="B27" s="367" t="inlineStr">
         <is>
           <t>Rutas de evacuación y puntos de encuentro señalizados</t>
         </is>
@@ -2952,11 +3019,11 @@
       <c r="E27" s="93" t="n"/>
       <c r="F27" s="93" t="n"/>
       <c r="G27" s="89" t="n"/>
-      <c r="H27" s="126" t="n"/>
-      <c r="I27" s="126" t="n"/>
-      <c r="J27" s="126" t="n"/>
-      <c r="K27" s="76" t="n"/>
-      <c r="L27" s="89" t="n"/>
+      <c r="H27" s="368" t="n"/>
+      <c r="I27" s="368" t="n"/>
+      <c r="J27" s="368" t="n"/>
+      <c r="K27" s="363" t="n"/>
+      <c r="L27" s="362" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="127">
       <c r="A28" s="162" t="inlineStr">
@@ -2977,10 +3044,10 @@
       <c r="L28" s="89" t="n"/>
     </row>
     <row r="29" ht="16.95" customHeight="1" s="127">
-      <c r="A29" s="126" t="n">
+      <c r="A29" s="366" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="72" t="inlineStr">
+      <c r="B29" s="367" t="inlineStr">
         <is>
           <t>Herramientas manuales en buen estado y bien almacenadas</t>
         </is>
@@ -2990,17 +3057,17 @@
       <c r="E29" s="93" t="n"/>
       <c r="F29" s="93" t="n"/>
       <c r="G29" s="89" t="n"/>
-      <c r="H29" s="126" t="n"/>
-      <c r="I29" s="126" t="n"/>
-      <c r="J29" s="126" t="n"/>
-      <c r="K29" s="76" t="n"/>
-      <c r="L29" s="89" t="n"/>
+      <c r="H29" s="368" t="n"/>
+      <c r="I29" s="368" t="n"/>
+      <c r="J29" s="368" t="n"/>
+      <c r="K29" s="363" t="n"/>
+      <c r="L29" s="362" t="n"/>
     </row>
     <row r="30" ht="16.95" customHeight="1" s="127">
-      <c r="A30" s="126" t="n">
+      <c r="A30" s="366" t="n">
         <v>9</v>
       </c>
-      <c r="B30" s="72" t="inlineStr">
+      <c r="B30" s="367" t="inlineStr">
         <is>
           <t>Equipos eléctricos con guardas y cables en buen estado</t>
         </is>
@@ -3010,17 +3077,17 @@
       <c r="E30" s="93" t="n"/>
       <c r="F30" s="93" t="n"/>
       <c r="G30" s="89" t="n"/>
-      <c r="H30" s="126" t="n"/>
-      <c r="I30" s="126" t="n"/>
-      <c r="J30" s="126" t="n"/>
-      <c r="K30" s="76" t="n"/>
-      <c r="L30" s="89" t="n"/>
+      <c r="H30" s="368" t="n"/>
+      <c r="I30" s="368" t="n"/>
+      <c r="J30" s="368" t="n"/>
+      <c r="K30" s="363" t="n"/>
+      <c r="L30" s="362" t="n"/>
     </row>
     <row r="31" ht="16.95" customHeight="1" s="127">
-      <c r="A31" s="126" t="n">
+      <c r="A31" s="366" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="72" t="inlineStr">
+      <c r="B31" s="367" t="inlineStr">
         <is>
           <t>Maquinaria con inspección preoperacional al día</t>
         </is>
@@ -3030,17 +3097,17 @@
       <c r="E31" s="93" t="n"/>
       <c r="F31" s="93" t="n"/>
       <c r="G31" s="89" t="n"/>
-      <c r="H31" s="126" t="n"/>
-      <c r="I31" s="126" t="n"/>
-      <c r="J31" s="126" t="n"/>
-      <c r="K31" s="76" t="n"/>
-      <c r="L31" s="89" t="n"/>
+      <c r="H31" s="368" t="n"/>
+      <c r="I31" s="368" t="n"/>
+      <c r="J31" s="368" t="n"/>
+      <c r="K31" s="363" t="n"/>
+      <c r="L31" s="362" t="n"/>
     </row>
     <row r="32" ht="16.95" customHeight="1" s="127">
-      <c r="A32" s="126" t="n">
+      <c r="A32" s="366" t="n">
         <v>11</v>
       </c>
-      <c r="B32" s="72" t="inlineStr">
+      <c r="B32" s="367" t="inlineStr">
         <is>
           <t>Equipos de izaje y accesorios certificados</t>
         </is>
@@ -3050,11 +3117,11 @@
       <c r="E32" s="93" t="n"/>
       <c r="F32" s="93" t="n"/>
       <c r="G32" s="89" t="n"/>
-      <c r="H32" s="126" t="n"/>
-      <c r="I32" s="126" t="n"/>
-      <c r="J32" s="126" t="n"/>
-      <c r="K32" s="76" t="n"/>
-      <c r="L32" s="89" t="n"/>
+      <c r="H32" s="368" t="n"/>
+      <c r="I32" s="368" t="n"/>
+      <c r="J32" s="368" t="n"/>
+      <c r="K32" s="363" t="n"/>
+      <c r="L32" s="362" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="127">
       <c r="A33" s="162" t="inlineStr">
@@ -3075,10 +3142,10 @@
       <c r="L33" s="89" t="n"/>
     </row>
     <row r="34" ht="16.95" customHeight="1" s="127">
-      <c r="A34" s="126" t="n">
+      <c r="A34" s="366" t="n">
         <v>12</v>
       </c>
-      <c r="B34" s="72" t="inlineStr">
+      <c r="B34" s="367" t="inlineStr">
         <is>
           <t>Tableros cerrados, rotulados y con protección</t>
         </is>
@@ -3088,17 +3155,17 @@
       <c r="E34" s="93" t="n"/>
       <c r="F34" s="93" t="n"/>
       <c r="G34" s="89" t="n"/>
-      <c r="H34" s="126" t="n"/>
-      <c r="I34" s="126" t="n"/>
-      <c r="J34" s="126" t="n"/>
-      <c r="K34" s="76" t="n"/>
-      <c r="L34" s="89" t="n"/>
+      <c r="H34" s="368" t="n"/>
+      <c r="I34" s="368" t="n"/>
+      <c r="J34" s="368" t="n"/>
+      <c r="K34" s="363" t="n"/>
+      <c r="L34" s="362" t="n"/>
     </row>
     <row r="35" ht="16.95" customHeight="1" s="127">
-      <c r="A35" s="126" t="n">
+      <c r="A35" s="366" t="n">
         <v>13</v>
       </c>
-      <c r="B35" s="72" t="inlineStr">
+      <c r="B35" s="367" t="inlineStr">
         <is>
           <t>Extensiones y empalmes en buen estado (sin cables pelados)</t>
         </is>
@@ -3108,17 +3175,17 @@
       <c r="E35" s="93" t="n"/>
       <c r="F35" s="93" t="n"/>
       <c r="G35" s="89" t="n"/>
-      <c r="H35" s="126" t="n"/>
-      <c r="I35" s="126" t="n"/>
-      <c r="J35" s="126" t="n"/>
-      <c r="K35" s="76" t="n"/>
-      <c r="L35" s="89" t="n"/>
+      <c r="H35" s="368" t="n"/>
+      <c r="I35" s="368" t="n"/>
+      <c r="J35" s="368" t="n"/>
+      <c r="K35" s="363" t="n"/>
+      <c r="L35" s="362" t="n"/>
     </row>
     <row r="36" ht="16.95" customHeight="1" s="127">
-      <c r="A36" s="126" t="n">
+      <c r="A36" s="366" t="n">
         <v>14</v>
       </c>
-      <c r="B36" s="72" t="inlineStr">
+      <c r="B36" s="367" t="inlineStr">
         <is>
           <t>Conexión a tierra y protección diferencial</t>
         </is>
@@ -3128,11 +3195,11 @@
       <c r="E36" s="93" t="n"/>
       <c r="F36" s="93" t="n"/>
       <c r="G36" s="89" t="n"/>
-      <c r="H36" s="126" t="n"/>
-      <c r="I36" s="126" t="n"/>
-      <c r="J36" s="126" t="n"/>
-      <c r="K36" s="76" t="n"/>
-      <c r="L36" s="89" t="n"/>
+      <c r="H36" s="368" t="n"/>
+      <c r="I36" s="368" t="n"/>
+      <c r="J36" s="368" t="n"/>
+      <c r="K36" s="363" t="n"/>
+      <c r="L36" s="362" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="127">
       <c r="A37" s="162" t="inlineStr">
@@ -3153,10 +3220,10 @@
       <c r="L37" s="89" t="n"/>
     </row>
     <row r="38" ht="16.95" customHeight="1" s="127">
-      <c r="A38" s="126" t="n">
+      <c r="A38" s="366" t="n">
         <v>15</v>
       </c>
-      <c r="B38" s="72" t="inlineStr">
+      <c r="B38" s="367" t="inlineStr">
         <is>
           <t>Andamios armados, certificados y con tarjeta de inspección</t>
         </is>
@@ -3166,17 +3233,17 @@
       <c r="E38" s="93" t="n"/>
       <c r="F38" s="93" t="n"/>
       <c r="G38" s="89" t="n"/>
-      <c r="H38" s="126" t="n"/>
-      <c r="I38" s="126" t="n"/>
-      <c r="J38" s="126" t="n"/>
-      <c r="K38" s="76" t="n"/>
-      <c r="L38" s="89" t="n"/>
+      <c r="H38" s="368" t="n"/>
+      <c r="I38" s="368" t="n"/>
+      <c r="J38" s="368" t="n"/>
+      <c r="K38" s="363" t="n"/>
+      <c r="L38" s="362" t="n"/>
     </row>
     <row r="39" ht="16.95" customHeight="1" s="127">
-      <c r="A39" s="126" t="n">
+      <c r="A39" s="366" t="n">
         <v>16</v>
       </c>
-      <c r="B39" s="72" t="inlineStr">
+      <c r="B39" s="367" t="inlineStr">
         <is>
           <t>Escaleras en buen estado y bien utilizadas</t>
         </is>
@@ -3186,17 +3253,17 @@
       <c r="E39" s="93" t="n"/>
       <c r="F39" s="93" t="n"/>
       <c r="G39" s="89" t="n"/>
-      <c r="H39" s="126" t="n"/>
-      <c r="I39" s="126" t="n"/>
-      <c r="J39" s="126" t="n"/>
-      <c r="K39" s="76" t="n"/>
-      <c r="L39" s="89" t="n"/>
+      <c r="H39" s="368" t="n"/>
+      <c r="I39" s="368" t="n"/>
+      <c r="J39" s="368" t="n"/>
+      <c r="K39" s="363" t="n"/>
+      <c r="L39" s="362" t="n"/>
     </row>
     <row r="40" ht="16.95" customHeight="1" s="127">
-      <c r="A40" s="126" t="n">
+      <c r="A40" s="366" t="n">
         <v>17</v>
       </c>
-      <c r="B40" s="72" t="inlineStr">
+      <c r="B40" s="367" t="inlineStr">
         <is>
           <t>Puntos de anclaje, líneas de vida y arneses inspeccionados</t>
         </is>
@@ -3206,11 +3273,11 @@
       <c r="E40" s="93" t="n"/>
       <c r="F40" s="93" t="n"/>
       <c r="G40" s="89" t="n"/>
-      <c r="H40" s="126" t="n"/>
-      <c r="I40" s="126" t="n"/>
-      <c r="J40" s="126" t="n"/>
-      <c r="K40" s="76" t="n"/>
-      <c r="L40" s="89" t="n"/>
+      <c r="H40" s="368" t="n"/>
+      <c r="I40" s="368" t="n"/>
+      <c r="J40" s="368" t="n"/>
+      <c r="K40" s="363" t="n"/>
+      <c r="L40" s="362" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="127">
       <c r="A41" s="162" t="inlineStr">
@@ -3231,10 +3298,10 @@
       <c r="L41" s="89" t="n"/>
     </row>
     <row r="42" ht="16.95" customHeight="1" s="127">
-      <c r="A42" s="126" t="n">
+      <c r="A42" s="366" t="n">
         <v>18</v>
       </c>
-      <c r="B42" s="72" t="inlineStr">
+      <c r="B42" s="367" t="inlineStr">
         <is>
           <t>Extintores vigentes, señalizados y accesibles</t>
         </is>
@@ -3244,17 +3311,17 @@
       <c r="E42" s="93" t="n"/>
       <c r="F42" s="93" t="n"/>
       <c r="G42" s="89" t="n"/>
-      <c r="H42" s="126" t="n"/>
-      <c r="I42" s="126" t="n"/>
-      <c r="J42" s="126" t="n"/>
-      <c r="K42" s="76" t="n"/>
-      <c r="L42" s="89" t="n"/>
+      <c r="H42" s="368" t="n"/>
+      <c r="I42" s="368" t="n"/>
+      <c r="J42" s="368" t="n"/>
+      <c r="K42" s="363" t="n"/>
+      <c r="L42" s="362" t="n"/>
     </row>
     <row r="43" ht="16.95" customHeight="1" s="127">
-      <c r="A43" s="126" t="n">
+      <c r="A43" s="366" t="n">
         <v>19</v>
       </c>
-      <c r="B43" s="72" t="inlineStr">
+      <c r="B43" s="367" t="inlineStr">
         <is>
           <t>Botiquín dotado y camilla disponible</t>
         </is>
@@ -3264,17 +3331,17 @@
       <c r="E43" s="93" t="n"/>
       <c r="F43" s="93" t="n"/>
       <c r="G43" s="89" t="n"/>
-      <c r="H43" s="126" t="n"/>
-      <c r="I43" s="126" t="n"/>
-      <c r="J43" s="126" t="n"/>
-      <c r="K43" s="76" t="n"/>
-      <c r="L43" s="89" t="n"/>
+      <c r="H43" s="368" t="n"/>
+      <c r="I43" s="368" t="n"/>
+      <c r="J43" s="368" t="n"/>
+      <c r="K43" s="363" t="n"/>
+      <c r="L43" s="362" t="n"/>
     </row>
     <row r="44" ht="16.95" customHeight="1" s="127">
-      <c r="A44" s="126" t="n">
+      <c r="A44" s="366" t="n">
         <v>20</v>
       </c>
-      <c r="B44" s="72" t="inlineStr">
+      <c r="B44" s="367" t="inlineStr">
         <is>
           <t>Directorio de emergencias visible y brigada conformada</t>
         </is>
@@ -3284,11 +3351,11 @@
       <c r="E44" s="93" t="n"/>
       <c r="F44" s="93" t="n"/>
       <c r="G44" s="89" t="n"/>
-      <c r="H44" s="126" t="n"/>
-      <c r="I44" s="126" t="n"/>
-      <c r="J44" s="126" t="n"/>
-      <c r="K44" s="76" t="n"/>
-      <c r="L44" s="89" t="n"/>
+      <c r="H44" s="368" t="n"/>
+      <c r="I44" s="368" t="n"/>
+      <c r="J44" s="368" t="n"/>
+      <c r="K44" s="363" t="n"/>
+      <c r="L44" s="362" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="127">
       <c r="A45" s="162" t="inlineStr">
@@ -3309,10 +3376,10 @@
       <c r="L45" s="89" t="n"/>
     </row>
     <row r="46" ht="16.95" customHeight="1" s="127">
-      <c r="A46" s="126" t="n">
+      <c r="A46" s="366" t="n">
         <v>21</v>
       </c>
-      <c r="B46" s="72" t="inlineStr">
+      <c r="B46" s="367" t="inlineStr">
         <is>
           <t>Personal con EPP completos y en buen estado</t>
         </is>
@@ -3322,17 +3389,17 @@
       <c r="E46" s="93" t="n"/>
       <c r="F46" s="93" t="n"/>
       <c r="G46" s="89" t="n"/>
-      <c r="H46" s="126" t="n"/>
-      <c r="I46" s="126" t="n"/>
-      <c r="J46" s="126" t="n"/>
-      <c r="K46" s="76" t="n"/>
-      <c r="L46" s="89" t="n"/>
+      <c r="H46" s="368" t="n"/>
+      <c r="I46" s="368" t="n"/>
+      <c r="J46" s="368" t="n"/>
+      <c r="K46" s="363" t="n"/>
+      <c r="L46" s="362" t="n"/>
     </row>
     <row r="47" ht="16.95" customHeight="1" s="127">
-      <c r="A47" s="126" t="n">
+      <c r="A47" s="366" t="n">
         <v>22</v>
       </c>
-      <c r="B47" s="72" t="inlineStr">
+      <c r="B47" s="367" t="inlineStr">
         <is>
           <t>Personal afiliado a seguridad social y con capacitación vigente</t>
         </is>
@@ -3342,17 +3409,17 @@
       <c r="E47" s="93" t="n"/>
       <c r="F47" s="93" t="n"/>
       <c r="G47" s="89" t="n"/>
-      <c r="H47" s="126" t="n"/>
-      <c r="I47" s="126" t="n"/>
-      <c r="J47" s="126" t="n"/>
-      <c r="K47" s="76" t="n"/>
-      <c r="L47" s="89" t="n"/>
+      <c r="H47" s="368" t="n"/>
+      <c r="I47" s="368" t="n"/>
+      <c r="J47" s="368" t="n"/>
+      <c r="K47" s="363" t="n"/>
+      <c r="L47" s="362" t="n"/>
     </row>
     <row r="48" ht="16.95" customHeight="1" s="127">
-      <c r="A48" s="126" t="n">
+      <c r="A48" s="366" t="n">
         <v>23</v>
       </c>
-      <c r="B48" s="72" t="inlineStr">
+      <c r="B48" s="367" t="inlineStr">
         <is>
           <t>Charla de seguridad realizada y registrada</t>
         </is>
@@ -3362,11 +3429,11 @@
       <c r="E48" s="93" t="n"/>
       <c r="F48" s="93" t="n"/>
       <c r="G48" s="89" t="n"/>
-      <c r="H48" s="126" t="n"/>
-      <c r="I48" s="126" t="n"/>
-      <c r="J48" s="126" t="n"/>
-      <c r="K48" s="76" t="n"/>
-      <c r="L48" s="89" t="n"/>
+      <c r="H48" s="368" t="n"/>
+      <c r="I48" s="368" t="n"/>
+      <c r="J48" s="368" t="n"/>
+      <c r="K48" s="363" t="n"/>
+      <c r="L48" s="362" t="n"/>
     </row>
     <row r="49" ht="21" customHeight="1" s="127">
       <c r="A49" s="310" t="inlineStr">
@@ -3481,164 +3548,164 @@
       </c>
     </row>
     <row r="53" ht="34.05" customHeight="1" s="127">
-      <c r="A53" s="126" t="n">
+      <c r="A53" s="366" t="n">
         <v>1</v>
       </c>
-      <c r="B53" s="72" t="n"/>
-      <c r="C53" s="93" t="n"/>
-      <c r="D53" s="89" t="n"/>
-      <c r="E53" s="126" t="n"/>
-      <c r="F53" s="72" t="n"/>
-      <c r="G53" s="93" t="n"/>
-      <c r="H53" s="89" t="n"/>
-      <c r="I53" s="76" t="n"/>
-      <c r="J53" s="89" t="n"/>
-      <c r="K53" s="23" t="n"/>
-      <c r="L53" s="126" t="n"/>
+      <c r="B53" s="363" t="n"/>
+      <c r="C53" s="361" t="n"/>
+      <c r="D53" s="362" t="n"/>
+      <c r="E53" s="368" t="n"/>
+      <c r="F53" s="363" t="n"/>
+      <c r="G53" s="361" t="n"/>
+      <c r="H53" s="362" t="n"/>
+      <c r="I53" s="363" t="n"/>
+      <c r="J53" s="362" t="n"/>
+      <c r="K53" s="369" t="n"/>
+      <c r="L53" s="368" t="n"/>
     </row>
     <row r="54" ht="34.05" customHeight="1" s="127">
-      <c r="A54" s="126" t="n">
+      <c r="A54" s="366" t="n">
         <v>2</v>
       </c>
-      <c r="B54" s="72" t="n"/>
-      <c r="C54" s="93" t="n"/>
-      <c r="D54" s="89" t="n"/>
-      <c r="E54" s="126" t="n"/>
-      <c r="F54" s="72" t="n"/>
-      <c r="G54" s="93" t="n"/>
-      <c r="H54" s="89" t="n"/>
-      <c r="I54" s="76" t="n"/>
-      <c r="J54" s="89" t="n"/>
-      <c r="K54" s="23" t="n"/>
-      <c r="L54" s="126" t="n"/>
+      <c r="B54" s="363" t="n"/>
+      <c r="C54" s="361" t="n"/>
+      <c r="D54" s="362" t="n"/>
+      <c r="E54" s="368" t="n"/>
+      <c r="F54" s="363" t="n"/>
+      <c r="G54" s="361" t="n"/>
+      <c r="H54" s="362" t="n"/>
+      <c r="I54" s="363" t="n"/>
+      <c r="J54" s="362" t="n"/>
+      <c r="K54" s="369" t="n"/>
+      <c r="L54" s="368" t="n"/>
     </row>
     <row r="55" ht="34.05" customHeight="1" s="127">
-      <c r="A55" s="126" t="n">
+      <c r="A55" s="366" t="n">
         <v>3</v>
       </c>
-      <c r="B55" s="72" t="n"/>
-      <c r="C55" s="93" t="n"/>
-      <c r="D55" s="89" t="n"/>
-      <c r="E55" s="126" t="n"/>
-      <c r="F55" s="72" t="n"/>
-      <c r="G55" s="93" t="n"/>
-      <c r="H55" s="89" t="n"/>
-      <c r="I55" s="76" t="n"/>
-      <c r="J55" s="89" t="n"/>
-      <c r="K55" s="23" t="n"/>
-      <c r="L55" s="126" t="n"/>
+      <c r="B55" s="363" t="n"/>
+      <c r="C55" s="361" t="n"/>
+      <c r="D55" s="362" t="n"/>
+      <c r="E55" s="368" t="n"/>
+      <c r="F55" s="363" t="n"/>
+      <c r="G55" s="361" t="n"/>
+      <c r="H55" s="362" t="n"/>
+      <c r="I55" s="363" t="n"/>
+      <c r="J55" s="362" t="n"/>
+      <c r="K55" s="369" t="n"/>
+      <c r="L55" s="368" t="n"/>
     </row>
     <row r="56" ht="34.05" customHeight="1" s="127">
-      <c r="A56" s="126" t="n">
+      <c r="A56" s="366" t="n">
         <v>4</v>
       </c>
-      <c r="B56" s="72" t="n"/>
-      <c r="C56" s="93" t="n"/>
-      <c r="D56" s="89" t="n"/>
-      <c r="E56" s="126" t="n"/>
-      <c r="F56" s="72" t="n"/>
-      <c r="G56" s="93" t="n"/>
-      <c r="H56" s="89" t="n"/>
-      <c r="I56" s="76" t="n"/>
-      <c r="J56" s="89" t="n"/>
-      <c r="K56" s="23" t="n"/>
-      <c r="L56" s="126" t="n"/>
+      <c r="B56" s="363" t="n"/>
+      <c r="C56" s="361" t="n"/>
+      <c r="D56" s="362" t="n"/>
+      <c r="E56" s="368" t="n"/>
+      <c r="F56" s="363" t="n"/>
+      <c r="G56" s="361" t="n"/>
+      <c r="H56" s="362" t="n"/>
+      <c r="I56" s="363" t="n"/>
+      <c r="J56" s="362" t="n"/>
+      <c r="K56" s="369" t="n"/>
+      <c r="L56" s="368" t="n"/>
     </row>
     <row r="57" ht="34.05" customHeight="1" s="127">
-      <c r="A57" s="126" t="n">
+      <c r="A57" s="366" t="n">
         <v>5</v>
       </c>
-      <c r="B57" s="72" t="n"/>
-      <c r="C57" s="93" t="n"/>
-      <c r="D57" s="89" t="n"/>
-      <c r="E57" s="126" t="n"/>
-      <c r="F57" s="72" t="n"/>
-      <c r="G57" s="93" t="n"/>
-      <c r="H57" s="89" t="n"/>
-      <c r="I57" s="76" t="n"/>
-      <c r="J57" s="89" t="n"/>
-      <c r="K57" s="23" t="n"/>
-      <c r="L57" s="126" t="n"/>
+      <c r="B57" s="363" t="n"/>
+      <c r="C57" s="361" t="n"/>
+      <c r="D57" s="362" t="n"/>
+      <c r="E57" s="368" t="n"/>
+      <c r="F57" s="363" t="n"/>
+      <c r="G57" s="361" t="n"/>
+      <c r="H57" s="362" t="n"/>
+      <c r="I57" s="363" t="n"/>
+      <c r="J57" s="362" t="n"/>
+      <c r="K57" s="369" t="n"/>
+      <c r="L57" s="368" t="n"/>
     </row>
     <row r="58" ht="34.05" customHeight="1" s="127">
-      <c r="A58" s="126" t="n">
+      <c r="A58" s="366" t="n">
         <v>6</v>
       </c>
-      <c r="B58" s="72" t="n"/>
-      <c r="C58" s="93" t="n"/>
-      <c r="D58" s="89" t="n"/>
-      <c r="E58" s="126" t="n"/>
-      <c r="F58" s="72" t="n"/>
-      <c r="G58" s="93" t="n"/>
-      <c r="H58" s="89" t="n"/>
-      <c r="I58" s="76" t="n"/>
-      <c r="J58" s="89" t="n"/>
-      <c r="K58" s="23" t="n"/>
-      <c r="L58" s="126" t="n"/>
+      <c r="B58" s="363" t="n"/>
+      <c r="C58" s="361" t="n"/>
+      <c r="D58" s="362" t="n"/>
+      <c r="E58" s="368" t="n"/>
+      <c r="F58" s="363" t="n"/>
+      <c r="G58" s="361" t="n"/>
+      <c r="H58" s="362" t="n"/>
+      <c r="I58" s="363" t="n"/>
+      <c r="J58" s="362" t="n"/>
+      <c r="K58" s="369" t="n"/>
+      <c r="L58" s="368" t="n"/>
     </row>
     <row r="59" ht="34.05" customHeight="1" s="127">
-      <c r="A59" s="126" t="n">
+      <c r="A59" s="366" t="n">
         <v>7</v>
       </c>
-      <c r="B59" s="72" t="n"/>
-      <c r="C59" s="93" t="n"/>
-      <c r="D59" s="89" t="n"/>
-      <c r="E59" s="126" t="n"/>
-      <c r="F59" s="72" t="n"/>
-      <c r="G59" s="93" t="n"/>
-      <c r="H59" s="89" t="n"/>
-      <c r="I59" s="76" t="n"/>
-      <c r="J59" s="89" t="n"/>
-      <c r="K59" s="23" t="n"/>
-      <c r="L59" s="126" t="n"/>
+      <c r="B59" s="363" t="n"/>
+      <c r="C59" s="361" t="n"/>
+      <c r="D59" s="362" t="n"/>
+      <c r="E59" s="368" t="n"/>
+      <c r="F59" s="363" t="n"/>
+      <c r="G59" s="361" t="n"/>
+      <c r="H59" s="362" t="n"/>
+      <c r="I59" s="363" t="n"/>
+      <c r="J59" s="362" t="n"/>
+      <c r="K59" s="369" t="n"/>
+      <c r="L59" s="368" t="n"/>
     </row>
     <row r="60" ht="34.05" customHeight="1" s="127">
-      <c r="A60" s="126" t="n">
+      <c r="A60" s="366" t="n">
         <v>8</v>
       </c>
-      <c r="B60" s="72" t="n"/>
-      <c r="C60" s="93" t="n"/>
-      <c r="D60" s="89" t="n"/>
-      <c r="E60" s="126" t="n"/>
-      <c r="F60" s="72" t="n"/>
-      <c r="G60" s="93" t="n"/>
-      <c r="H60" s="89" t="n"/>
-      <c r="I60" s="76" t="n"/>
-      <c r="J60" s="89" t="n"/>
-      <c r="K60" s="23" t="n"/>
-      <c r="L60" s="126" t="n"/>
+      <c r="B60" s="363" t="n"/>
+      <c r="C60" s="361" t="n"/>
+      <c r="D60" s="362" t="n"/>
+      <c r="E60" s="368" t="n"/>
+      <c r="F60" s="363" t="n"/>
+      <c r="G60" s="361" t="n"/>
+      <c r="H60" s="362" t="n"/>
+      <c r="I60" s="363" t="n"/>
+      <c r="J60" s="362" t="n"/>
+      <c r="K60" s="369" t="n"/>
+      <c r="L60" s="368" t="n"/>
     </row>
     <row r="61" ht="34.05" customHeight="1" s="127">
-      <c r="A61" s="126" t="n">
+      <c r="A61" s="366" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="72" t="n"/>
-      <c r="C61" s="93" t="n"/>
-      <c r="D61" s="89" t="n"/>
-      <c r="E61" s="126" t="n"/>
-      <c r="F61" s="72" t="n"/>
-      <c r="G61" s="93" t="n"/>
-      <c r="H61" s="89" t="n"/>
-      <c r="I61" s="76" t="n"/>
-      <c r="J61" s="89" t="n"/>
-      <c r="K61" s="23" t="n"/>
-      <c r="L61" s="126" t="n"/>
+      <c r="B61" s="363" t="n"/>
+      <c r="C61" s="361" t="n"/>
+      <c r="D61" s="362" t="n"/>
+      <c r="E61" s="368" t="n"/>
+      <c r="F61" s="363" t="n"/>
+      <c r="G61" s="361" t="n"/>
+      <c r="H61" s="362" t="n"/>
+      <c r="I61" s="363" t="n"/>
+      <c r="J61" s="362" t="n"/>
+      <c r="K61" s="369" t="n"/>
+      <c r="L61" s="368" t="n"/>
     </row>
     <row r="62" ht="34.05" customHeight="1" s="127">
-      <c r="A62" s="126" t="n">
+      <c r="A62" s="366" t="n">
         <v>10</v>
       </c>
-      <c r="B62" s="72" t="n"/>
-      <c r="C62" s="93" t="n"/>
-      <c r="D62" s="89" t="n"/>
-      <c r="E62" s="126" t="n"/>
-      <c r="F62" s="72" t="n"/>
-      <c r="G62" s="93" t="n"/>
-      <c r="H62" s="89" t="n"/>
-      <c r="I62" s="76" t="n"/>
-      <c r="J62" s="89" t="n"/>
-      <c r="K62" s="23" t="n"/>
-      <c r="L62" s="126" t="n"/>
+      <c r="B62" s="363" t="n"/>
+      <c r="C62" s="361" t="n"/>
+      <c r="D62" s="362" t="n"/>
+      <c r="E62" s="368" t="n"/>
+      <c r="F62" s="363" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="363" t="n"/>
+      <c r="J62" s="362" t="n"/>
+      <c r="K62" s="369" t="n"/>
+      <c r="L62" s="368" t="n"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="127">
       <c r="A63" s="137" t="inlineStr">
@@ -3659,32 +3726,32 @@
       <c r="L63" s="97" t="n"/>
     </row>
     <row r="64" ht="30" customHeight="1" s="127">
-      <c r="A64" s="100" t="n"/>
-      <c r="B64" s="104" t="n"/>
-      <c r="C64" s="104" t="n"/>
-      <c r="D64" s="104" t="n"/>
-      <c r="E64" s="104" t="n"/>
-      <c r="F64" s="104" t="n"/>
-      <c r="G64" s="104" t="n"/>
-      <c r="H64" s="104" t="n"/>
-      <c r="I64" s="104" t="n"/>
-      <c r="J64" s="104" t="n"/>
-      <c r="K64" s="104" t="n"/>
-      <c r="L64" s="94" t="n"/>
+      <c r="A64" s="370" t="n"/>
+      <c r="B64" s="371" t="n"/>
+      <c r="C64" s="371" t="n"/>
+      <c r="D64" s="371" t="n"/>
+      <c r="E64" s="371" t="n"/>
+      <c r="F64" s="371" t="n"/>
+      <c r="G64" s="371" t="n"/>
+      <c r="H64" s="371" t="n"/>
+      <c r="I64" s="371" t="n"/>
+      <c r="J64" s="371" t="n"/>
+      <c r="K64" s="371" t="n"/>
+      <c r="L64" s="372" t="n"/>
     </row>
     <row r="65" ht="30" customHeight="1" s="127">
-      <c r="A65" s="96" t="n"/>
-      <c r="B65" s="98" t="n"/>
-      <c r="C65" s="98" t="n"/>
-      <c r="D65" s="98" t="n"/>
-      <c r="E65" s="98" t="n"/>
-      <c r="F65" s="98" t="n"/>
-      <c r="G65" s="98" t="n"/>
-      <c r="H65" s="98" t="n"/>
-      <c r="I65" s="98" t="n"/>
-      <c r="J65" s="98" t="n"/>
-      <c r="K65" s="98" t="n"/>
-      <c r="L65" s="97" t="n"/>
+      <c r="A65" s="373" t="n"/>
+      <c r="B65" s="374" t="n"/>
+      <c r="C65" s="374" t="n"/>
+      <c r="D65" s="374" t="n"/>
+      <c r="E65" s="374" t="n"/>
+      <c r="F65" s="374" t="n"/>
+      <c r="G65" s="374" t="n"/>
+      <c r="H65" s="374" t="n"/>
+      <c r="I65" s="374" t="n"/>
+      <c r="J65" s="374" t="n"/>
+      <c r="K65" s="374" t="n"/>
+      <c r="L65" s="375" t="n"/>
     </row>
     <row r="66" ht="16.5" customHeight="1" s="127">
       <c r="A66" s="227" t="inlineStr">
@@ -3723,20 +3790,20 @@
         </is>
       </c>
       <c r="B68" s="97" t="n"/>
-      <c r="C68" s="301" t="n"/>
-      <c r="D68" s="98" t="n"/>
-      <c r="E68" s="98" t="n"/>
-      <c r="F68" s="97" t="n"/>
+      <c r="C68" s="376" t="n"/>
+      <c r="D68" s="374" t="n"/>
+      <c r="E68" s="374" t="n"/>
+      <c r="F68" s="375" t="n"/>
       <c r="G68" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="H68" s="97" t="n"/>
-      <c r="I68" s="301" t="n"/>
-      <c r="J68" s="98" t="n"/>
-      <c r="K68" s="98" t="n"/>
-      <c r="L68" s="97" t="n"/>
+      <c r="I68" s="376" t="n"/>
+      <c r="J68" s="374" t="n"/>
+      <c r="K68" s="374" t="n"/>
+      <c r="L68" s="375" t="n"/>
     </row>
     <row r="69" ht="21" customHeight="1" s="127">
       <c r="A69" s="70" t="inlineStr">
@@ -3745,20 +3812,20 @@
         </is>
       </c>
       <c r="B69" s="89" t="n"/>
-      <c r="C69" s="68" t="n"/>
-      <c r="D69" s="93" t="n"/>
-      <c r="E69" s="93" t="n"/>
-      <c r="F69" s="89" t="n"/>
+      <c r="C69" s="363" t="n"/>
+      <c r="D69" s="361" t="n"/>
+      <c r="E69" s="361" t="n"/>
+      <c r="F69" s="362" t="n"/>
       <c r="G69" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="H69" s="89" t="n"/>
-      <c r="I69" s="68" t="n"/>
-      <c r="J69" s="93" t="n"/>
-      <c r="K69" s="93" t="n"/>
-      <c r="L69" s="89" t="n"/>
+      <c r="I69" s="363" t="n"/>
+      <c r="J69" s="361" t="n"/>
+      <c r="K69" s="361" t="n"/>
+      <c r="L69" s="362" t="n"/>
     </row>
     <row r="70" ht="21" customHeight="1" s="127">
       <c r="A70" s="70" t="inlineStr">
@@ -3767,20 +3834,20 @@
         </is>
       </c>
       <c r="B70" s="89" t="n"/>
-      <c r="C70" s="68" t="n"/>
-      <c r="D70" s="93" t="n"/>
-      <c r="E70" s="93" t="n"/>
-      <c r="F70" s="89" t="n"/>
+      <c r="C70" s="363" t="n"/>
+      <c r="D70" s="361" t="n"/>
+      <c r="E70" s="361" t="n"/>
+      <c r="F70" s="362" t="n"/>
       <c r="G70" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="H70" s="89" t="n"/>
-      <c r="I70" s="68" t="n"/>
-      <c r="J70" s="93" t="n"/>
-      <c r="K70" s="93" t="n"/>
-      <c r="L70" s="89" t="n"/>
+      <c r="I70" s="363" t="n"/>
+      <c r="J70" s="361" t="n"/>
+      <c r="K70" s="361" t="n"/>
+      <c r="L70" s="362" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="25" t="inlineStr">
@@ -3794,6 +3861,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="143">
     <mergeCell ref="K49:L49"/>
     <mergeCell ref="B60:D60"/>
